--- a/每日股價行情表.xlsx
+++ b/每日股價行情表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\as75315907\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54679E41-9469-4430-9182-665B62EC6B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453FD4B8-926B-43AB-A93E-C4C0043085A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8880" yWindow="1560" windowWidth="26430" windowHeight="16035" tabRatio="885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IR_updated (PC HOME)" sheetId="80" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2812" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2683" uniqueCount="173">
   <si>
     <t>eslite.ir</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -999,56 +999,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>走勢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF252525"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF004BBB"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>明細</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>新聞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF252525"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF004BBB"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>技術</t>
-    </r>
-  </si>
-  <si>
     <t>瓦　城</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1068,7 +1018,7 @@
     <numFmt numFmtId="182" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="183" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="38" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="新細明體"/>
@@ -1287,41 +1237,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF252525"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF004BBB"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFEA313F"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF004BBB"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF139506"/>
       <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -1745,7 +1660,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2113,53 +2028,11 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="4" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="35" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="33" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="37" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="33" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="33" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -2198,13 +2071,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2259,13 +2132,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2321,13 +2194,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2382,13 +2255,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2444,13 +2317,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2506,13 +2379,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2567,13 +2440,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2629,13 +2502,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2690,13 +2563,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2752,13 +2625,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2813,13 +2686,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2875,13 +2748,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2936,13 +2809,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2998,13 +2871,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3059,13 +2932,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3121,13 +2994,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3182,13 +3055,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3244,13 +3117,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3305,13 +3178,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3366,13 +3239,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3428,13 +3301,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3489,13 +3362,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3550,13 +3423,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3612,13 +3485,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3673,13 +3546,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3734,13 +3607,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3796,13 +3669,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3857,13 +3730,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3918,13 +3791,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3980,13 +3853,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4041,13 +3914,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4103,13 +3976,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4164,13 +4037,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4225,13 +4098,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4287,13 +4160,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4348,13 +4221,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4409,13 +4282,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4471,13 +4344,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4532,13 +4405,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4593,13 +4466,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4655,13 +4528,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4716,13 +4589,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4778,13 +4651,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4839,13 +4712,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4900,13 +4773,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4962,13 +4835,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5023,13 +4896,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5084,13 +4957,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5146,13 +5019,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5207,13 +5080,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5268,13 +5141,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5330,13 +5203,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5391,13 +5264,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5452,13 +5325,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5514,13 +5387,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5575,13 +5448,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5636,13 +5509,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5698,13 +5571,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5759,13 +5632,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5821,13 +5694,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5882,13 +5755,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5944,13 +5817,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6005,13 +5878,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6067,13 +5940,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6129,13 +6002,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6190,13 +6063,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6252,13 +6125,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6313,13 +6186,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6375,13 +6248,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6436,13 +6309,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6498,13 +6371,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6560,13 +6433,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6621,13 +6494,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6683,13 +6556,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6744,13 +6617,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6806,13 +6679,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6867,13 +6740,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6928,13 +6801,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6990,13 +6863,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7051,13 +6924,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7112,13 +6985,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7174,13 +7047,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7235,13 +7108,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7296,13 +7169,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7358,13 +7231,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7419,13 +7292,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7480,13 +7353,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7542,13 +7415,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7603,13 +7476,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7665,13 +7538,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7726,13 +7599,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7787,13 +7660,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7849,13 +7722,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7910,13 +7783,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7971,13 +7844,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8033,13 +7906,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8094,13 +7967,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8155,13 +8028,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8217,13 +8090,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8278,13 +8151,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8340,13 +8213,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8401,13 +8274,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8462,13 +8335,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8524,13 +8397,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8585,13 +8458,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8646,13 +8519,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8708,13 +8581,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8769,13 +8642,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8830,13 +8703,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8892,13 +8765,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8953,13 +8826,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9014,13 +8887,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9076,13 +8949,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9137,13 +9010,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9198,13 +9071,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9260,13 +9133,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9321,13 +9194,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9383,13 +9256,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9444,13 +9317,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9506,13 +9379,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9567,13 +9440,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9629,13 +9502,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9691,13 +9564,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9752,13 +9625,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9814,13 +9687,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9875,13 +9748,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9937,13 +9810,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9998,13 +9871,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10060,13 +9933,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10122,13 +9995,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10183,13 +10056,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10245,13 +10118,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10306,13 +10179,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10368,13 +10241,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10429,13 +10302,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10490,13 +10363,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10552,13 +10425,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10613,13 +10486,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10674,13 +10547,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10736,13 +10609,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10797,13 +10670,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10858,13 +10731,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10920,13 +10793,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10981,13 +10854,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -11042,13 +10915,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -11104,13 +10977,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -11165,13 +11038,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -11227,13 +11100,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -11288,13 +11161,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -11349,13 +11222,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -11411,13 +11284,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -11472,13 +11345,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -11533,13 +11406,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -11595,13 +11468,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -11656,13 +11529,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -11717,13 +11590,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -11779,13 +11652,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -11840,13 +11713,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -11901,13 +11774,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -11963,13 +11836,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -12024,13 +11897,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -12085,13 +11958,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -12147,13 +12020,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -12208,13 +12081,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -12269,13 +12142,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -12331,13 +12204,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -12392,13 +12265,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -12453,13 +12326,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -12515,13 +12388,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -12576,13 +12449,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -12637,13 +12510,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -12699,13 +12572,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -12760,13 +12633,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -12821,13 +12694,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -12883,13 +12756,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -12944,13 +12817,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -13432,7 +13305,7 @@
   <sheetPr codeName="工作表2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA96"/>
+  <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5" style="14" customWidth="1"/>
@@ -13465,17 +13338,17 @@
       </c>
     </row>
     <row r="2" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="149"/>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149"/>
-      <c r="J2" s="149"/>
-      <c r="K2" s="149"/>
-      <c r="L2" s="149"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
       <c r="O2" s="15"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -13491,7 +13364,7 @@
       </c>
       <c r="L3" s="19">
         <f ca="1">NOW()</f>
-        <v>46067.954631944442</v>
+        <v>46068.898451041663</v>
       </c>
       <c r="O3" s="101" t="s">
         <v>56</v>
@@ -13671,7 +13544,7 @@
       <c r="D11" s="46" t="str">
         <f ca="1">"今日收盤"
 &amp;MONTH(L3)&amp;"/"&amp;DAY(L3)</f>
-        <v>今日收盤2/14</v>
+        <v>今日收盤2/15</v>
       </c>
       <c r="E11" s="47" t="str">
         <f>"前一交易日
@@ -13730,41 +13603,41 @@
         <v>79</v>
       </c>
       <c r="C13" s="57"/>
-      <c r="D13" s="60">
-        <f>D59</f>
-        <v>52</v>
-      </c>
-      <c r="E13" s="60">
-        <f>I60</f>
-        <v>52</v>
-      </c>
-      <c r="F13" s="61">
+      <c r="D13" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E13" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F13" s="61" t="e">
         <f>D13-E13</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="62">
+        <v>#REF!</v>
+      </c>
+      <c r="G13" s="62" t="e">
         <f>F13/E13</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="63">
-        <f>I59</f>
-        <v>52.4</v>
-      </c>
-      <c r="I13" s="60">
-        <f>J60</f>
-        <v>51.6</v>
-      </c>
-      <c r="J13" s="60">
-        <f>J59</f>
-        <v>52.4</v>
-      </c>
-      <c r="K13" s="64">
-        <f>D60</f>
-        <v>9</v>
-      </c>
-      <c r="L13" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H13" s="63" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I13" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J13" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K13" s="64" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L13" s="64" t="e">
         <f>+O13*D13</f>
-        <v>2464.2618000000002</v>
+        <v>#REF!</v>
       </c>
       <c r="M13" s="51"/>
       <c r="N13" s="51"/>
@@ -13782,41 +13655,41 @@
         <v>80</v>
       </c>
       <c r="C14" s="66"/>
-      <c r="D14" s="60">
-        <f>D63</f>
-        <v>257</v>
-      </c>
-      <c r="E14" s="60">
-        <f>I64</f>
-        <v>257.5</v>
-      </c>
-      <c r="F14" s="61">
+      <c r="D14" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E14" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F14" s="61" t="e">
         <f t="shared" ref="F14:F30" si="0">D14-E14</f>
-        <v>-0.5</v>
-      </c>
-      <c r="G14" s="62">
+        <v>#REF!</v>
+      </c>
+      <c r="G14" s="62" t="e">
         <f>F14/E14</f>
-        <v>-1.9417475728155339E-3</v>
-      </c>
-      <c r="H14" s="63">
-        <f>I63</f>
-        <v>259</v>
-      </c>
-      <c r="I14" s="60">
-        <f>J64</f>
-        <v>257</v>
-      </c>
-      <c r="J14" s="60">
-        <f>J63</f>
-        <v>259.5</v>
-      </c>
-      <c r="K14" s="73">
-        <f>D64</f>
-        <v>1218</v>
-      </c>
-      <c r="L14" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H14" s="63" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I14" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J14" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K14" s="73" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L14" s="64" t="e">
         <f>+O14*D14</f>
-        <v>267182.85399999999</v>
+        <v>#REF!</v>
       </c>
       <c r="M14" s="51"/>
       <c r="N14" s="51"/>
@@ -13834,41 +13707,41 @@
         <v>117</v>
       </c>
       <c r="C15" s="57"/>
-      <c r="D15" s="71">
-        <f>D49</f>
-        <v>196.5</v>
-      </c>
-      <c r="E15" s="71">
-        <f>$I$50</f>
-        <v>197</v>
-      </c>
-      <c r="F15" s="61">
+      <c r="D15" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E15" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F15" s="61" t="e">
         <f>D15-E15</f>
-        <v>-0.5</v>
-      </c>
-      <c r="G15" s="62">
+        <v>#REF!</v>
+      </c>
+      <c r="G15" s="62" t="e">
         <f>F15/E15</f>
-        <v>-2.5380710659898475E-3</v>
-      </c>
-      <c r="H15" s="72">
-        <f>$I$49</f>
-        <v>197.5</v>
-      </c>
-      <c r="I15" s="60">
-        <f>J50</f>
-        <v>196.5</v>
-      </c>
-      <c r="J15" s="71">
-        <f>$J$49</f>
-        <v>197.5</v>
-      </c>
-      <c r="K15" s="73">
-        <f>$D$50</f>
-        <v>66</v>
-      </c>
-      <c r="L15" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H15" s="72" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I15" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J15" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K15" s="73" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L15" s="64" t="e">
         <f>D15*O15</f>
-        <v>43862.73</v>
+        <v>#REF!</v>
       </c>
       <c r="M15" s="74"/>
       <c r="N15" s="74"/>
@@ -13886,41 +13759,41 @@
         <v>124</v>
       </c>
       <c r="C16" s="57"/>
-      <c r="D16" s="71">
-        <f>D47</f>
-        <v>40</v>
-      </c>
-      <c r="E16" s="71">
-        <f>I48</f>
-        <v>40</v>
-      </c>
-      <c r="F16" s="61">
+      <c r="D16" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E16" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F16" s="61" t="e">
         <f>D16-E16</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="62">
+        <v>#REF!</v>
+      </c>
+      <c r="G16" s="62" t="e">
         <f>F16/E16</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="72">
-        <f>I47</f>
-        <v>40</v>
-      </c>
-      <c r="I16" s="60">
-        <f>J48</f>
-        <v>40</v>
-      </c>
-      <c r="J16" s="71">
-        <f>J47</f>
-        <v>40</v>
-      </c>
-      <c r="K16" s="73">
-        <f>D48</f>
-        <v>1</v>
-      </c>
-      <c r="L16" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H16" s="72" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I16" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J16" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K16" s="73" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L16" s="64" t="e">
         <f>D16*O16</f>
-        <v>2700</v>
+        <v>#REF!</v>
       </c>
       <c r="M16" s="74"/>
       <c r="N16" s="74"/>
@@ -13938,41 +13811,41 @@
         <v>81</v>
       </c>
       <c r="C17" s="66"/>
-      <c r="D17" s="60">
-        <f>D65</f>
-        <v>25.35</v>
-      </c>
-      <c r="E17" s="60">
-        <f>I66</f>
-        <v>25.4</v>
-      </c>
-      <c r="F17" s="61">
+      <c r="D17" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E17" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F17" s="61" t="e">
         <f t="shared" si="0"/>
-        <v>-4.9999999999997158E-2</v>
-      </c>
-      <c r="G17" s="62">
+        <v>#REF!</v>
+      </c>
+      <c r="G17" s="62" t="e">
         <f t="shared" ref="G17:G22" si="1">F17/E17</f>
-        <v>-1.9685039370077621E-3</v>
-      </c>
-      <c r="H17" s="63">
-        <f>I65</f>
-        <v>25.4</v>
-      </c>
-      <c r="I17" s="60">
-        <f>J66</f>
-        <v>25.15</v>
-      </c>
-      <c r="J17" s="60">
-        <f>J65</f>
-        <v>25.7</v>
-      </c>
-      <c r="K17" s="64">
-        <f>D66</f>
-        <v>1803</v>
-      </c>
-      <c r="L17" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H17" s="63" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I17" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J17" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K17" s="64" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L17" s="64" t="e">
         <f>+O17*D17</f>
-        <v>35919.45435</v>
+        <v>#REF!</v>
       </c>
       <c r="M17" s="67"/>
       <c r="N17" s="67"/>
@@ -13990,41 +13863,41 @@
         <v>82</v>
       </c>
       <c r="C18" s="57"/>
-      <c r="D18" s="60">
-        <f>D67</f>
-        <v>489.5</v>
-      </c>
-      <c r="E18" s="60">
-        <f>I68</f>
-        <v>495</v>
-      </c>
-      <c r="F18" s="61">
+      <c r="D18" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E18" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F18" s="61" t="e">
         <f t="shared" si="0"/>
-        <v>-5.5</v>
-      </c>
-      <c r="G18" s="62">
+        <v>#REF!</v>
+      </c>
+      <c r="G18" s="62" t="e">
         <f t="shared" si="1"/>
-        <v>-1.1111111111111112E-2</v>
-      </c>
-      <c r="H18" s="63">
-        <f>I67</f>
-        <v>496.5</v>
-      </c>
-      <c r="I18" s="60">
-        <f>J68</f>
-        <v>489.5</v>
-      </c>
-      <c r="J18" s="60">
-        <f>J67</f>
-        <v>500</v>
-      </c>
-      <c r="K18" s="64">
-        <f>D68</f>
-        <v>298</v>
-      </c>
-      <c r="L18" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H18" s="63" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I18" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J18" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K18" s="64" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L18" s="64" t="e">
         <f>+O18*D18</f>
-        <v>51366.172000000006</v>
+        <v>#REF!</v>
       </c>
       <c r="O18" s="65">
         <v>104.93600000000001</v>
@@ -14040,41 +13913,41 @@
         <v>83</v>
       </c>
       <c r="C19" s="57"/>
-      <c r="D19" s="60">
-        <f>D69</f>
-        <v>9.61</v>
-      </c>
-      <c r="E19" s="60">
-        <f>I70</f>
-        <v>9.86</v>
-      </c>
-      <c r="F19" s="61">
+      <c r="D19" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E19" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F19" s="61" t="e">
         <f t="shared" si="0"/>
-        <v>-0.25</v>
-      </c>
-      <c r="G19" s="62">
+        <v>#REF!</v>
+      </c>
+      <c r="G19" s="62" t="e">
         <f>F19/E19</f>
-        <v>-2.5354969574036514E-2</v>
-      </c>
-      <c r="H19" s="63">
-        <f>I69</f>
-        <v>9.8800000000000008</v>
-      </c>
-      <c r="I19" s="60">
-        <f>J70</f>
-        <v>9.59</v>
-      </c>
-      <c r="J19" s="60">
-        <f>J69</f>
-        <v>9.9</v>
-      </c>
-      <c r="K19" s="64">
-        <f>D70</f>
-        <v>561</v>
-      </c>
-      <c r="L19" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H19" s="63" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I19" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J19" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K19" s="64" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L19" s="64" t="e">
         <f>+O19*D19</f>
-        <v>1879.0529099999999</v>
+        <v>#REF!</v>
       </c>
       <c r="O19" s="65">
         <v>195.53100000000001</v>
@@ -14090,41 +13963,41 @@
         <v>84</v>
       </c>
       <c r="C20" s="57"/>
-      <c r="D20" s="71">
-        <f>D61</f>
-        <v>34.950000000000003</v>
-      </c>
-      <c r="E20" s="60">
-        <f>I62</f>
-        <v>35.17</v>
-      </c>
-      <c r="F20" s="61">
+      <c r="D20" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E20" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F20" s="61" t="e">
         <f>D20-E20</f>
-        <v>-0.21999999999999886</v>
-      </c>
-      <c r="G20" s="62">
+        <v>#REF!</v>
+      </c>
+      <c r="G20" s="62" t="e">
         <f>F20/E20</f>
-        <v>-6.2553312482228843E-3</v>
-      </c>
-      <c r="H20" s="63">
-        <f>I61</f>
-        <v>34.9</v>
-      </c>
-      <c r="I20" s="60">
-        <f>J62</f>
-        <v>34.85</v>
-      </c>
-      <c r="J20" s="60">
-        <f>J61</f>
-        <v>35</v>
-      </c>
-      <c r="K20" s="64">
-        <f>D62</f>
-        <v>12</v>
-      </c>
-      <c r="L20" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H20" s="63" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I20" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J20" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K20" s="64" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L20" s="64" t="e">
         <f>O20*D20</f>
-        <v>2097</v>
+        <v>#REF!</v>
       </c>
       <c r="O20" s="65">
         <v>60</v>
@@ -14140,41 +14013,41 @@
         <v>85</v>
       </c>
       <c r="C21" s="66"/>
-      <c r="D21" s="60">
-        <f>D71</f>
-        <v>216.5</v>
-      </c>
-      <c r="E21" s="60">
-        <f>I72</f>
-        <v>213.5</v>
-      </c>
-      <c r="F21" s="61">
+      <c r="D21" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E21" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F21" s="61" t="e">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G21" s="62">
+        <v>#REF!</v>
+      </c>
+      <c r="G21" s="62" t="e">
         <f t="shared" si="1"/>
-        <v>1.405152224824356E-2</v>
-      </c>
-      <c r="H21" s="63">
-        <f>I71</f>
-        <v>215</v>
-      </c>
-      <c r="I21" s="60">
-        <f>J72</f>
-        <v>212</v>
-      </c>
-      <c r="J21" s="60">
-        <f>J71</f>
-        <v>217</v>
-      </c>
-      <c r="K21" s="64">
-        <f>D72</f>
-        <v>679</v>
-      </c>
-      <c r="L21" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H21" s="63" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I21" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J21" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K21" s="64" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L21" s="64" t="e">
         <f t="shared" ref="L21:L28" si="2">+O21*D21</f>
-        <v>27582.749500000002</v>
+        <v>#REF!</v>
       </c>
       <c r="M21" s="67"/>
       <c r="N21" s="67"/>
@@ -14192,41 +14065,41 @@
         <v>86</v>
       </c>
       <c r="C22" s="66"/>
-      <c r="D22" s="60">
-        <f>D73</f>
-        <v>51.4</v>
-      </c>
-      <c r="E22" s="60">
-        <f>I74</f>
-        <v>51.4</v>
-      </c>
-      <c r="F22" s="61">
+      <c r="D22" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E22" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F22" s="61" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="62">
+        <v>#REF!</v>
+      </c>
+      <c r="G22" s="62" t="e">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="63">
-        <f>I73</f>
-        <v>51.2</v>
-      </c>
-      <c r="I22" s="60">
-        <f>J74</f>
-        <v>51.2</v>
-      </c>
-      <c r="J22" s="60">
-        <f>J73</f>
-        <v>51.6</v>
-      </c>
-      <c r="K22" s="64">
-        <f>D74</f>
-        <v>60</v>
-      </c>
-      <c r="L22" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H22" s="63" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I22" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J22" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K22" s="64" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L22" s="64" t="e">
         <f t="shared" si="2"/>
-        <v>18859.808430199999</v>
+        <v>#REF!</v>
       </c>
       <c r="M22" s="67"/>
       <c r="N22" s="67"/>
@@ -14244,41 +14117,41 @@
         <v>87</v>
       </c>
       <c r="C23" s="66"/>
-      <c r="D23" s="60">
-        <f>D55</f>
-        <v>48.3</v>
-      </c>
-      <c r="E23" s="60">
-        <f>I56</f>
-        <v>48.6</v>
-      </c>
-      <c r="F23" s="61">
+      <c r="D23" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E23" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F23" s="61" t="e">
         <f>D23-E23</f>
-        <v>-0.30000000000000426</v>
-      </c>
-      <c r="G23" s="62">
+        <v>#REF!</v>
+      </c>
+      <c r="G23" s="62" t="e">
         <f>F23/E23</f>
-        <v>-6.1728395061729268E-3</v>
-      </c>
-      <c r="H23" s="63">
-        <f>I55</f>
-        <v>48.65</v>
-      </c>
-      <c r="I23" s="60">
-        <f>J56</f>
-        <v>48.05</v>
-      </c>
-      <c r="J23" s="60">
-        <f>J55</f>
-        <v>48.65</v>
-      </c>
-      <c r="K23" s="64">
-        <f>D56</f>
-        <v>83</v>
-      </c>
-      <c r="L23" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H23" s="63" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I23" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J23" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K23" s="64" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L23" s="64" t="e">
         <f t="shared" si="2"/>
-        <v>4420.7057999999997</v>
+        <v>#REF!</v>
       </c>
       <c r="M23" s="67"/>
       <c r="N23" s="67"/>
@@ -14296,41 +14169,41 @@
         <v>115</v>
       </c>
       <c r="C24" s="66"/>
-      <c r="D24" s="60">
-        <f>D57</f>
-        <v>58.6</v>
-      </c>
-      <c r="E24" s="60">
-        <f>I58</f>
-        <v>59.1</v>
-      </c>
-      <c r="F24" s="68">
+      <c r="D24" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E24" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F24" s="68" t="e">
         <f t="shared" si="0"/>
-        <v>-0.5</v>
-      </c>
-      <c r="G24" s="69">
+        <v>#REF!</v>
+      </c>
+      <c r="G24" s="69" t="e">
         <f>F24/E24</f>
-        <v>-8.4602368866328256E-3</v>
-      </c>
-      <c r="H24" s="63">
-        <f>I57</f>
-        <v>60.2</v>
-      </c>
-      <c r="I24" s="60">
-        <f>J58</f>
-        <v>58.5</v>
-      </c>
-      <c r="J24" s="60">
-        <f>J57</f>
-        <v>60.2</v>
-      </c>
-      <c r="K24" s="64">
-        <f>D58</f>
-        <v>118</v>
-      </c>
-      <c r="L24" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H24" s="63" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I24" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J24" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K24" s="64" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L24" s="64" t="e">
         <f t="shared" si="2"/>
-        <v>6198.6494000000002</v>
+        <v>#REF!</v>
       </c>
       <c r="M24" s="67"/>
       <c r="N24" s="67"/>
@@ -14348,41 +14221,41 @@
         <v>88</v>
       </c>
       <c r="C25" s="57"/>
-      <c r="D25" s="71">
-        <f>D75</f>
-        <v>96</v>
-      </c>
-      <c r="E25" s="71">
-        <f>I76</f>
-        <v>96.5</v>
-      </c>
-      <c r="F25" s="68">
+      <c r="D25" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E25" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F25" s="68" t="e">
         <f t="shared" si="0"/>
-        <v>-0.5</v>
-      </c>
-      <c r="G25" s="69">
+        <v>#REF!</v>
+      </c>
+      <c r="G25" s="69" t="e">
         <f t="shared" ref="G25:G31" si="3">F25/E25</f>
-        <v>-5.1813471502590676E-3</v>
-      </c>
-      <c r="H25" s="72">
-        <f>I75</f>
-        <v>96.5</v>
-      </c>
-      <c r="I25" s="60">
-        <f>J76</f>
-        <v>95.5</v>
-      </c>
-      <c r="J25" s="71">
-        <f>J75</f>
-        <v>96.5</v>
-      </c>
-      <c r="K25" s="73">
-        <f>D76</f>
-        <v>207</v>
-      </c>
-      <c r="L25" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H25" s="72" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I25" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J25" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K25" s="73" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L25" s="64" t="e">
         <f t="shared" si="2"/>
-        <v>17280</v>
+        <v>#REF!</v>
       </c>
       <c r="M25" s="74"/>
       <c r="N25" s="74"/>
@@ -14400,41 +14273,41 @@
         <v>89</v>
       </c>
       <c r="C26" s="57"/>
-      <c r="D26" s="71">
-        <f>D77</f>
-        <v>232.5</v>
-      </c>
-      <c r="E26" s="71">
-        <f>I78</f>
-        <v>233</v>
-      </c>
-      <c r="F26" s="68">
+      <c r="D26" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E26" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F26" s="68" t="e">
         <f t="shared" si="0"/>
-        <v>-0.5</v>
-      </c>
-      <c r="G26" s="69">
+        <v>#REF!</v>
+      </c>
+      <c r="G26" s="69" t="e">
         <f t="shared" si="3"/>
-        <v>-2.1459227467811159E-3</v>
-      </c>
-      <c r="H26" s="72">
-        <f>I77</f>
-        <v>233.5</v>
-      </c>
-      <c r="I26" s="71">
-        <f>J78</f>
-        <v>231</v>
-      </c>
-      <c r="J26" s="71">
-        <f>J77</f>
-        <v>233.5</v>
-      </c>
-      <c r="K26" s="73">
-        <f>D78</f>
-        <v>256</v>
-      </c>
-      <c r="L26" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H26" s="72" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I26" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J26" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K26" s="73" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L26" s="64" t="e">
         <f t="shared" si="2"/>
-        <v>19634.857499999998</v>
+        <v>#REF!</v>
       </c>
       <c r="M26" s="74"/>
       <c r="N26" s="74"/>
@@ -14452,41 +14325,41 @@
         <v>90</v>
       </c>
       <c r="C27" s="57"/>
-      <c r="D27" s="71" t="str">
-        <f>D79</f>
-        <v>－－</v>
-      </c>
-      <c r="E27" s="71">
-        <f>I80</f>
-        <v>64.7</v>
+      <c r="D27" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E27" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="F27" s="68" t="e">
         <f>D27-E27</f>
-        <v>#VALUE!</v>
+        <v>#REF!</v>
       </c>
       <c r="G27" s="69" t="e">
         <f>F27/E27</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H27" s="72" t="str">
-        <f>I79</f>
-        <v>－－</v>
-      </c>
-      <c r="I27" s="71" t="str">
-        <f>J80</f>
-        <v>－－</v>
-      </c>
-      <c r="J27" s="71" t="str">
-        <f>J79</f>
-        <v>－－</v>
-      </c>
-      <c r="K27" s="73" t="str">
-        <f>D80</f>
-        <v>－－</v>
+        <v>#REF!</v>
+      </c>
+      <c r="H27" s="72" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I27" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J27" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K27" s="73" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="L27" s="64" t="e">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v>#REF!</v>
       </c>
       <c r="M27" s="74"/>
       <c r="N27" s="74"/>
@@ -14501,44 +14374,44 @@
         <v>2729</v>
       </c>
       <c r="B28" s="57" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C28" s="57"/>
-      <c r="D28" s="71">
-        <f>D81</f>
-        <v>200.5</v>
-      </c>
-      <c r="E28" s="71">
-        <f>I82</f>
-        <v>200</v>
-      </c>
-      <c r="F28" s="68">
+      <c r="D28" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E28" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F28" s="68" t="e">
         <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="G28" s="69">
+        <v>#REF!</v>
+      </c>
+      <c r="G28" s="69" t="e">
         <f t="shared" si="3"/>
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="H28" s="72">
-        <f>I81</f>
-        <v>199</v>
-      </c>
-      <c r="I28" s="71">
-        <f>J82</f>
-        <v>199</v>
-      </c>
-      <c r="J28" s="71">
-        <f>J81</f>
-        <v>200.5</v>
-      </c>
-      <c r="K28" s="73">
-        <f>D82</f>
-        <v>13</v>
-      </c>
-      <c r="L28" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H28" s="72" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I28" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J28" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K28" s="73" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L28" s="64" t="e">
         <f t="shared" si="2"/>
-        <v>7919.9504999999999</v>
+        <v>#REF!</v>
       </c>
       <c r="M28" s="74"/>
       <c r="N28" s="74"/>
@@ -14556,41 +14429,41 @@
         <v>121</v>
       </c>
       <c r="C29" s="57"/>
-      <c r="D29" s="71">
-        <f>D45</f>
-        <v>114</v>
-      </c>
-      <c r="E29" s="71">
-        <f>I46</f>
-        <v>112.86</v>
-      </c>
-      <c r="F29" s="68">
+      <c r="D29" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E29" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F29" s="68" t="e">
         <f>D29-E29</f>
-        <v>1.1400000000000006</v>
-      </c>
-      <c r="G29" s="69">
+        <v>#REF!</v>
+      </c>
+      <c r="G29" s="69" t="e">
         <f>F29/E29</f>
-        <v>1.0101010101010105E-2</v>
-      </c>
-      <c r="H29" s="72">
-        <f>I45</f>
-        <v>114</v>
-      </c>
-      <c r="I29" s="71">
-        <f>J46</f>
-        <v>111.5</v>
-      </c>
-      <c r="J29" s="71">
-        <f>J45</f>
-        <v>114.5</v>
-      </c>
-      <c r="K29" s="73">
-        <f>D46</f>
-        <v>21</v>
-      </c>
-      <c r="L29" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H29" s="72" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I29" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J29" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K29" s="73" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L29" s="64" t="e">
         <f>+D29*O29</f>
-        <v>2335.417794</v>
+        <v>#REF!</v>
       </c>
       <c r="M29" s="74"/>
       <c r="N29" s="74"/>
@@ -14608,41 +14481,41 @@
         <v>91</v>
       </c>
       <c r="C30" s="57"/>
-      <c r="D30" s="71">
-        <f>D87</f>
-        <v>42.2</v>
-      </c>
-      <c r="E30" s="71">
-        <f>I88</f>
-        <v>42.65</v>
-      </c>
-      <c r="F30" s="68">
+      <c r="D30" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E30" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F30" s="68" t="e">
         <f t="shared" si="0"/>
-        <v>-0.44999999999999574</v>
-      </c>
-      <c r="G30" s="69">
+        <v>#REF!</v>
+      </c>
+      <c r="G30" s="69" t="e">
         <f t="shared" si="3"/>
-        <v>-1.0550996483001073E-2</v>
-      </c>
-      <c r="H30" s="72">
-        <f>I87</f>
-        <v>43.05</v>
-      </c>
-      <c r="I30" s="71">
-        <f>J88</f>
-        <v>42.2</v>
-      </c>
-      <c r="J30" s="71">
-        <f>J87</f>
-        <v>43.2</v>
-      </c>
-      <c r="K30" s="73">
-        <f>D88</f>
-        <v>384</v>
-      </c>
-      <c r="L30" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H30" s="72" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I30" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J30" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K30" s="73" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L30" s="64" t="e">
         <f>D30*O30</f>
-        <v>8678.3034000000007</v>
+        <v>#REF!</v>
       </c>
       <c r="M30" s="74"/>
       <c r="N30" s="74"/>
@@ -14660,41 +14533,41 @@
         <v>92</v>
       </c>
       <c r="C31" s="57"/>
-      <c r="D31" s="71">
-        <f>D85</f>
-        <v>50.5</v>
-      </c>
-      <c r="E31" s="71">
-        <f>I86</f>
-        <v>51.6</v>
-      </c>
-      <c r="F31" s="68">
+      <c r="D31" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E31" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F31" s="68" t="e">
         <f>D31-E31</f>
-        <v>-1.1000000000000014</v>
-      </c>
-      <c r="G31" s="69">
+        <v>#REF!</v>
+      </c>
+      <c r="G31" s="69" t="e">
         <f t="shared" si="3"/>
-        <v>-2.1317829457364369E-2</v>
-      </c>
-      <c r="H31" s="72">
-        <f>I85</f>
-        <v>52.2</v>
-      </c>
-      <c r="I31" s="71">
-        <f>J86</f>
-        <v>50.2</v>
-      </c>
-      <c r="J31" s="71">
-        <f>J85</f>
-        <v>52.2</v>
-      </c>
-      <c r="K31" s="73">
-        <f>D86</f>
-        <v>1198</v>
-      </c>
-      <c r="L31" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H31" s="72" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I31" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J31" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K31" s="73" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L31" s="64" t="e">
         <f>+O31*D31</f>
-        <v>31929.281500000001</v>
+        <v>#REF!</v>
       </c>
       <c r="M31" s="74"/>
       <c r="N31" s="74"/>
@@ -14712,41 +14585,41 @@
         <v>113</v>
       </c>
       <c r="C32" s="57"/>
-      <c r="D32" s="71">
-        <f>D89</f>
-        <v>362.5</v>
-      </c>
-      <c r="E32" s="71">
-        <f>I90</f>
-        <v>365</v>
-      </c>
-      <c r="F32" s="68">
+      <c r="D32" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E32" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F32" s="68" t="e">
         <f>D32-E32</f>
-        <v>-2.5</v>
-      </c>
-      <c r="G32" s="69">
+        <v>#REF!</v>
+      </c>
+      <c r="G32" s="69" t="e">
         <f>F32/E32</f>
-        <v>-6.8493150684931503E-3</v>
-      </c>
-      <c r="H32" s="72">
-        <f>I89</f>
-        <v>365</v>
-      </c>
-      <c r="I32" s="71">
-        <f>J90</f>
-        <v>361.5</v>
-      </c>
-      <c r="J32" s="71">
-        <f>J89</f>
-        <v>366</v>
-      </c>
-      <c r="K32" s="73">
-        <f>D90</f>
-        <v>70</v>
-      </c>
-      <c r="L32" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H32" s="72" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I32" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J32" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K32" s="73" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L32" s="64" t="e">
         <f>+O32*D32</f>
-        <v>91479.412500000006</v>
+        <v>#REF!</v>
       </c>
       <c r="M32" s="74"/>
       <c r="N32" s="74"/>
@@ -14764,41 +14637,41 @@
         <v>118</v>
       </c>
       <c r="C33" s="57"/>
-      <c r="D33" s="71">
-        <f>D53</f>
-        <v>13.4</v>
-      </c>
-      <c r="E33" s="71">
-        <f>I54</f>
-        <v>13.55</v>
-      </c>
-      <c r="F33" s="68">
+      <c r="D33" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E33" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F33" s="68" t="e">
         <f>D33-E33</f>
-        <v>-0.15000000000000036</v>
-      </c>
-      <c r="G33" s="69">
+        <v>#REF!</v>
+      </c>
+      <c r="G33" s="69" t="e">
         <f>F33/E33</f>
-        <v>-1.1070110701107036E-2</v>
-      </c>
-      <c r="H33" s="72">
-        <f>I53</f>
-        <v>13.3</v>
-      </c>
-      <c r="I33" s="71">
-        <f>J54</f>
-        <v>13.3</v>
-      </c>
-      <c r="J33" s="71">
-        <f>J53</f>
-        <v>13.45</v>
-      </c>
-      <c r="K33" s="73">
-        <f>D54</f>
-        <v>13</v>
-      </c>
-      <c r="L33" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H33" s="72" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I33" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J33" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K33" s="73" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L33" s="64" t="e">
         <f>+O33*D33</f>
-        <v>859.89140000000009</v>
+        <v>#REF!</v>
       </c>
       <c r="M33" s="74"/>
       <c r="N33" s="74"/>
@@ -14816,41 +14689,41 @@
         <v>119</v>
       </c>
       <c r="C34" s="57"/>
-      <c r="D34" s="71">
-        <f>$D$51</f>
-        <v>92.2</v>
-      </c>
-      <c r="E34" s="71">
-        <f>$I$52</f>
-        <v>91</v>
-      </c>
-      <c r="F34" s="68">
+      <c r="D34" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E34" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F34" s="68" t="e">
         <f>D34-E34</f>
-        <v>1.2000000000000028</v>
-      </c>
-      <c r="G34" s="69">
+        <v>#REF!</v>
+      </c>
+      <c r="G34" s="69" t="e">
         <f>F34/E34</f>
-        <v>1.3186813186813218E-2</v>
-      </c>
-      <c r="H34" s="72">
-        <f>$I$51</f>
-        <v>91.2</v>
-      </c>
-      <c r="I34" s="71">
-        <f>J52</f>
-        <v>91</v>
-      </c>
-      <c r="J34" s="71">
-        <f>$J$51</f>
-        <v>92.5</v>
-      </c>
-      <c r="K34" s="73">
-        <f>$D$52</f>
-        <v>311</v>
-      </c>
-      <c r="L34" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H34" s="72" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I34" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J34" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K34" s="73" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L34" s="64" t="e">
         <f>+O34*D34</f>
-        <v>11117.2916</v>
+        <v>#REF!</v>
       </c>
       <c r="M34" s="74"/>
       <c r="N34" s="74"/>
@@ -14868,41 +14741,41 @@
         <v>140</v>
       </c>
       <c r="C35" s="57"/>
-      <c r="D35" s="71">
-        <f>D91</f>
-        <v>720</v>
-      </c>
-      <c r="E35" s="71">
-        <f>I92</f>
-        <v>693</v>
-      </c>
-      <c r="F35" s="68">
+      <c r="D35" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E35" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F35" s="68" t="e">
         <f>D35-E35</f>
-        <v>27</v>
-      </c>
-      <c r="G35" s="69">
+        <v>#REF!</v>
+      </c>
+      <c r="G35" s="69" t="e">
         <f>F35/E35</f>
-        <v>3.896103896103896E-2</v>
-      </c>
-      <c r="H35" s="72">
-        <f>I91</f>
-        <v>695</v>
-      </c>
-      <c r="I35" s="71">
-        <f>J92</f>
-        <v>692</v>
-      </c>
-      <c r="J35" s="71">
-        <f>J91</f>
-        <v>730</v>
-      </c>
-      <c r="K35" s="73">
-        <f>D92</f>
-        <v>166</v>
-      </c>
-      <c r="L35" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H35" s="72" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I35" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J35" s="71" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K35" s="73" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L35" s="64" t="e">
         <f>+O35*D35</f>
-        <v>48960</v>
+        <v>#REF!</v>
       </c>
       <c r="M35" s="74"/>
       <c r="N35" s="74"/>
@@ -14960,41 +14833,41 @@
         <v>94</v>
       </c>
       <c r="C38" s="66"/>
-      <c r="D38" s="60">
-        <f>F94</f>
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="E38" s="60">
-        <f>M94</f>
-        <v>0.09</v>
-      </c>
-      <c r="F38" s="61">
+      <c r="D38" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E38" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F38" s="61" t="e">
         <f>D38-E38</f>
-        <v>5.0000000000000044E-3</v>
-      </c>
-      <c r="G38" s="62">
+        <v>#REF!</v>
+      </c>
+      <c r="G38" s="62" t="e">
         <f>F38/E38</f>
-        <v>5.5555555555555608E-2</v>
-      </c>
-      <c r="H38" s="63">
-        <f>J94</f>
-        <v>0.09</v>
-      </c>
-      <c r="I38" s="60">
-        <f>L94</f>
-        <v>0.09</v>
-      </c>
-      <c r="J38" s="60">
-        <f>K94</f>
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="K38" s="64">
-        <f>I94</f>
-        <v>1728</v>
-      </c>
-      <c r="L38" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H38" s="63" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I38" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J38" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K38" s="64" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L38" s="64" t="e">
         <f>+O38*D38</f>
-        <v>250.28054000000003</v>
+        <v>#REF!</v>
       </c>
       <c r="M38" s="67"/>
       <c r="N38" s="67"/>
@@ -15012,41 +14885,41 @@
         <v>95</v>
       </c>
       <c r="C39" s="66"/>
-      <c r="D39" s="60">
-        <f>F95</f>
-        <v>0.315</v>
-      </c>
-      <c r="E39" s="60">
-        <f>M95</f>
-        <v>0.315</v>
-      </c>
-      <c r="F39" s="61">
+      <c r="D39" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E39" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F39" s="61" t="e">
         <f>D39-E39</f>
-        <v>0</v>
-      </c>
-      <c r="G39" s="77">
+        <v>#REF!</v>
+      </c>
+      <c r="G39" s="77" t="e">
         <f>F39/E39</f>
-        <v>0</v>
-      </c>
-      <c r="H39" s="63">
-        <f>J95</f>
-        <v>0.32</v>
-      </c>
-      <c r="I39" s="60">
-        <f>L95</f>
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="J39" s="60">
-        <f>K95</f>
-        <v>0.32</v>
-      </c>
-      <c r="K39" s="64">
-        <f>I95</f>
-        <v>47</v>
-      </c>
-      <c r="L39" s="64">
+        <v>#REF!</v>
+      </c>
+      <c r="H39" s="63" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I39" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J39" s="60" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K39" s="64" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L39" s="64" t="e">
         <f>+O39*D39</f>
-        <v>531.13567499999999</v>
+        <v>#REF!</v>
       </c>
       <c r="M39" s="67"/>
       <c r="N39" s="67"/>
@@ -15071,45 +14944,22 @@
       <c r="M41" s="78"/>
       <c r="N41" s="78"/>
     </row>
-    <row r="42" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="124"/>
-      <c r="B42" s="125" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="126" t="s">
-        <v>96</v>
-      </c>
-      <c r="D42" s="127" t="s">
-        <v>97</v>
-      </c>
-      <c r="E42" s="126" t="s">
-        <v>71</v>
-      </c>
-      <c r="F42" s="126" t="s">
-        <v>98</v>
-      </c>
-      <c r="G42" s="126" t="s">
-        <v>99</v>
-      </c>
-      <c r="H42" s="126" t="s">
-        <v>100</v>
-      </c>
-      <c r="I42" s="128" t="s">
-        <v>73</v>
-      </c>
-      <c r="J42" s="128" t="s">
-        <v>101</v>
-      </c>
-      <c r="K42" s="126" t="s">
-        <v>102</v>
-      </c>
-      <c r="L42" s="126" t="s">
-        <v>103</v>
-      </c>
-      <c r="M42" s="126"/>
-      <c r="N42" s="129"/>
-      <c r="O42" s="92"/>
-      <c r="P42" s="75"/>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B42" s="142"/>
+      <c r="C42" s="142"/>
+      <c r="D42" s="142"/>
+      <c r="E42" s="142"/>
+      <c r="F42" s="142"/>
+      <c r="G42" s="142"/>
+      <c r="H42" s="142"/>
+      <c r="I42" s="142"/>
+      <c r="J42" s="142"/>
+      <c r="K42" s="142"/>
+      <c r="L42" s="142"/>
+      <c r="M42" s="142"/>
+      <c r="N42" s="142"/>
+      <c r="O42" s="142"/>
+      <c r="P42" s="142"/>
       <c r="Q42" s="75"/>
       <c r="R42" s="75"/>
       <c r="S42" s="75"/>
@@ -15120,2748 +14970,26 @@
       <c r="X42" s="75"/>
       <c r="Y42" s="75"/>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A43" s="124"/>
-      <c r="B43" s="130"/>
-      <c r="C43" s="131"/>
-      <c r="D43" s="127" t="s">
-        <v>104</v>
-      </c>
-      <c r="E43" s="126" t="s">
-        <v>105</v>
-      </c>
-      <c r="F43" s="126" t="s">
-        <v>106</v>
-      </c>
-      <c r="G43" s="126" t="s">
-        <v>107</v>
-      </c>
-      <c r="H43" s="126" t="s">
-        <v>108</v>
-      </c>
-      <c r="I43" s="128" t="s">
-        <v>109</v>
-      </c>
-      <c r="J43" s="128" t="s">
-        <v>74</v>
-      </c>
-      <c r="K43" s="126" t="s">
-        <v>110</v>
-      </c>
-      <c r="L43" s="126" t="s">
-        <v>111</v>
-      </c>
-      <c r="M43" s="126"/>
-      <c r="N43" s="129"/>
-      <c r="O43" s="92"/>
-      <c r="P43" s="75"/>
-      <c r="Q43" s="75"/>
-      <c r="R43" s="75"/>
-      <c r="S43" s="75"/>
-      <c r="T43" s="75"/>
-      <c r="U43" s="75"/>
-      <c r="V43" s="75"/>
-      <c r="W43" s="75"/>
-      <c r="X43" s="75"/>
-      <c r="Y43" s="75"/>
-    </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A44" s="132" t="s">
-        <v>10</v>
-      </c>
-      <c r="B44" s="132"/>
-      <c r="C44" s="132"/>
-      <c r="D44" s="132"/>
-      <c r="E44" s="132"/>
-      <c r="F44" s="132"/>
-      <c r="G44" s="132"/>
-      <c r="H44" s="132"/>
-      <c r="I44" s="132"/>
-      <c r="J44" s="132"/>
-      <c r="K44" s="132"/>
-      <c r="L44" s="132"/>
-      <c r="M44" s="132"/>
-      <c r="N44" s="132"/>
-      <c r="O44" s="92"/>
-      <c r="P44" s="75"/>
-      <c r="Q44" s="75"/>
-      <c r="R44" s="75"/>
-      <c r="S44" s="75"/>
-      <c r="T44" s="75"/>
-      <c r="U44" s="75"/>
-      <c r="V44" s="75"/>
-      <c r="W44" s="75"/>
-      <c r="X44" s="75"/>
-      <c r="Y44" s="75"/>
-    </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A45" s="151"/>
-      <c r="B45" s="141" t="s">
-        <v>123</v>
-      </c>
-      <c r="C45" s="152">
-        <v>0.62172453703703701</v>
-      </c>
-      <c r="D45" s="142">
-        <v>114</v>
-      </c>
-      <c r="E45" s="142">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="F45" s="142">
-        <v>113</v>
-      </c>
-      <c r="G45" s="142">
-        <v>114</v>
-      </c>
-      <c r="H45" s="148">
-        <v>10</v>
-      </c>
-      <c r="I45" s="142">
-        <v>114</v>
-      </c>
-      <c r="J45" s="142">
-        <v>114.5</v>
-      </c>
-      <c r="K45" s="148" t="s">
-        <v>14</v>
-      </c>
-      <c r="L45" s="148">
-        <v>188</v>
-      </c>
-      <c r="M45" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N45" s="153"/>
-      <c r="O45" s="92"/>
-      <c r="P45" s="75"/>
-      <c r="Q45" s="75"/>
-      <c r="R45" s="75"/>
-      <c r="S45" s="75"/>
-      <c r="T45" s="75"/>
-      <c r="U45" s="75"/>
-      <c r="V45" s="75"/>
-      <c r="W45" s="75"/>
-      <c r="X45" s="75"/>
-      <c r="Y45" s="75"/>
-    </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A46" s="151"/>
-      <c r="B46" s="141">
-        <v>-2758</v>
-      </c>
-      <c r="C46" s="152"/>
-      <c r="D46" s="148">
-        <v>21</v>
-      </c>
-      <c r="E46" s="144">
-        <v>1.01E-2</v>
-      </c>
-      <c r="F46" s="145">
-        <v>2000</v>
-      </c>
-      <c r="G46" s="145">
-        <v>4474</v>
-      </c>
-      <c r="H46" s="148">
-        <v>5</v>
-      </c>
-      <c r="I46" s="142">
-        <v>112.86</v>
-      </c>
-      <c r="J46" s="146">
-        <v>111.5</v>
-      </c>
-      <c r="K46" s="148" t="s">
-        <v>14</v>
-      </c>
-      <c r="L46" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M46" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N46" s="153"/>
-      <c r="O46" s="92"/>
-      <c r="P46" s="75"/>
-      <c r="Q46" s="75"/>
-      <c r="R46" s="75"/>
-      <c r="S46" s="75"/>
-      <c r="T46" s="75"/>
-      <c r="U46" s="75"/>
-      <c r="V46" s="75"/>
-      <c r="W46" s="75"/>
-      <c r="X46" s="75"/>
-      <c r="Y46" s="75"/>
-    </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A47" s="151"/>
-      <c r="B47" s="141" t="s">
-        <v>124</v>
-      </c>
-      <c r="C47" s="152">
-        <v>0.44223379629629633</v>
-      </c>
-      <c r="D47" s="148">
-        <v>40</v>
-      </c>
-      <c r="E47" s="148" t="s">
-        <v>14</v>
-      </c>
-      <c r="F47" s="142">
-        <v>40.049999999999997</v>
-      </c>
-      <c r="G47" s="142">
-        <v>40.4</v>
-      </c>
-      <c r="H47" s="148" t="s">
-        <v>14</v>
-      </c>
-      <c r="I47" s="148">
-        <v>40</v>
-      </c>
-      <c r="J47" s="148">
-        <v>40</v>
-      </c>
-      <c r="K47" s="148">
-        <v>44</v>
-      </c>
-      <c r="L47" s="148">
-        <v>84</v>
-      </c>
-      <c r="M47" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N47" s="153"/>
-      <c r="O47" s="92"/>
-      <c r="P47" s="75"/>
-      <c r="Q47" s="75"/>
-      <c r="R47" s="75"/>
-      <c r="S47" s="75"/>
-      <c r="T47" s="75"/>
-      <c r="U47" s="75"/>
-      <c r="V47" s="75"/>
-      <c r="W47" s="75"/>
-      <c r="X47" s="75"/>
-      <c r="Y47" s="75"/>
-    </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A48" s="151"/>
-      <c r="B48" s="141">
-        <v>-2945</v>
-      </c>
-      <c r="C48" s="152"/>
-      <c r="D48" s="148">
-        <v>1</v>
-      </c>
-      <c r="E48" s="148" t="s">
-        <v>14</v>
-      </c>
-      <c r="F48" s="148">
-        <v>1</v>
-      </c>
-      <c r="G48" s="148">
-        <v>1</v>
-      </c>
-      <c r="H48" s="148">
-        <v>1</v>
-      </c>
-      <c r="I48" s="148">
-        <v>40</v>
-      </c>
-      <c r="J48" s="148">
-        <v>40</v>
-      </c>
-      <c r="K48" s="148">
-        <v>36</v>
-      </c>
-      <c r="L48" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M48" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N48" s="153"/>
-      <c r="O48" s="92"/>
-      <c r="P48" s="75"/>
-      <c r="Q48" s="75"/>
-      <c r="R48" s="75"/>
-      <c r="S48" s="75"/>
-      <c r="T48" s="75"/>
-      <c r="U48" s="75"/>
-      <c r="V48" s="75"/>
-      <c r="W48" s="75"/>
-      <c r="X48" s="75"/>
-      <c r="Y48" s="75"/>
-    </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A49" s="151"/>
-      <c r="B49" s="141" t="s">
-        <v>122</v>
-      </c>
-      <c r="C49" s="152">
-        <v>0.5625</v>
-      </c>
-      <c r="D49" s="146">
-        <v>196.5</v>
-      </c>
-      <c r="E49" s="146">
-        <v>-0.5</v>
-      </c>
-      <c r="F49" s="146">
-        <v>196.5</v>
-      </c>
-      <c r="G49" s="148">
-        <v>197</v>
-      </c>
-      <c r="H49" s="148">
-        <v>37</v>
-      </c>
-      <c r="I49" s="142">
-        <v>197.5</v>
-      </c>
-      <c r="J49" s="142">
-        <v>197.5</v>
-      </c>
-      <c r="K49" s="148">
-        <v>216.5</v>
-      </c>
-      <c r="L49" s="148">
-        <v>0</v>
-      </c>
-      <c r="M49" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N49" s="153"/>
-      <c r="O49" s="92"/>
-      <c r="P49" s="75"/>
-      <c r="Q49" s="75"/>
-      <c r="R49" s="75"/>
-      <c r="S49" s="75"/>
-      <c r="T49" s="75"/>
-      <c r="U49" s="75"/>
-      <c r="V49" s="75"/>
-      <c r="W49" s="75"/>
-      <c r="X49" s="75"/>
-      <c r="Y49" s="75"/>
-    </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A50" s="151"/>
-      <c r="B50" s="141">
-        <v>-5903</v>
-      </c>
-      <c r="C50" s="152"/>
-      <c r="D50" s="148">
-        <v>66</v>
-      </c>
-      <c r="E50" s="147">
-        <v>-2.5000000000000001E-3</v>
-      </c>
-      <c r="F50" s="148">
-        <v>16</v>
-      </c>
-      <c r="G50" s="148">
-        <v>13</v>
-      </c>
-      <c r="H50" s="148">
-        <v>28</v>
-      </c>
-      <c r="I50" s="148">
-        <v>197</v>
-      </c>
-      <c r="J50" s="146">
-        <v>196.5</v>
-      </c>
-      <c r="K50" s="148">
-        <v>177.5</v>
-      </c>
-      <c r="L50" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M50" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N50" s="153"/>
-      <c r="O50" s="92"/>
-      <c r="P50" s="75"/>
-      <c r="Q50" s="75"/>
-      <c r="R50" s="75"/>
-      <c r="S50" s="75"/>
-      <c r="T50" s="75"/>
-      <c r="U50" s="75"/>
-      <c r="V50" s="75"/>
-      <c r="W50" s="75"/>
-      <c r="X50" s="75"/>
-      <c r="Y50" s="75"/>
-    </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A51" s="151"/>
-      <c r="B51" s="141" t="s">
-        <v>116</v>
-      </c>
-      <c r="C51" s="152">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D51" s="142">
-        <v>92.2</v>
-      </c>
-      <c r="E51" s="142">
-        <v>1.2</v>
-      </c>
-      <c r="F51" s="142">
-        <v>92</v>
-      </c>
-      <c r="G51" s="142">
-        <v>92.2</v>
-      </c>
-      <c r="H51" s="148">
-        <v>118</v>
-      </c>
-      <c r="I51" s="142">
-        <v>91.2</v>
-      </c>
-      <c r="J51" s="142">
-        <v>92.5</v>
-      </c>
-      <c r="K51" s="148">
-        <v>100</v>
-      </c>
-      <c r="L51" s="148">
-        <v>396</v>
-      </c>
-      <c r="M51" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N51" s="153"/>
-      <c r="O51" s="92"/>
-      <c r="P51" s="75"/>
-      <c r="Q51" s="75"/>
-      <c r="R51" s="75"/>
-      <c r="S51" s="75"/>
-      <c r="T51" s="75"/>
-      <c r="U51" s="75"/>
-      <c r="V51" s="75"/>
-      <c r="W51" s="75"/>
-      <c r="X51" s="75"/>
-      <c r="Y51" s="75"/>
-    </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A52" s="151"/>
-      <c r="B52" s="141">
-        <v>-6741</v>
-      </c>
-      <c r="C52" s="152"/>
-      <c r="D52" s="148">
-        <v>311</v>
-      </c>
-      <c r="E52" s="144">
-        <v>1.32E-2</v>
-      </c>
-      <c r="F52" s="148">
-        <v>3</v>
-      </c>
-      <c r="G52" s="148">
-        <v>3</v>
-      </c>
-      <c r="H52" s="148">
-        <v>189</v>
-      </c>
-      <c r="I52" s="148">
-        <v>91</v>
-      </c>
-      <c r="J52" s="148">
-        <v>91</v>
-      </c>
-      <c r="K52" s="148">
-        <v>81.900000000000006</v>
-      </c>
-      <c r="L52" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M52" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N52" s="153"/>
-      <c r="O52" s="92"/>
-      <c r="P52" s="75"/>
-      <c r="Q52" s="75"/>
-      <c r="R52" s="75"/>
-      <c r="S52" s="75"/>
-      <c r="T52" s="75"/>
-      <c r="U52" s="75"/>
-      <c r="V52" s="75"/>
-      <c r="W52" s="75"/>
-      <c r="X52" s="75"/>
-      <c r="Y52" s="75"/>
-    </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A53" s="151"/>
-      <c r="B53" s="141" t="s">
-        <v>112</v>
-      </c>
-      <c r="C53" s="152">
-        <v>0.55574074074074076</v>
-      </c>
-      <c r="D53" s="146">
-        <v>13.4</v>
-      </c>
-      <c r="E53" s="146">
-        <v>-0.15</v>
-      </c>
-      <c r="F53" s="146">
-        <v>13.45</v>
-      </c>
-      <c r="G53" s="142">
-        <v>13.75</v>
-      </c>
-      <c r="H53" s="148">
-        <v>12</v>
-      </c>
-      <c r="I53" s="146">
-        <v>13.3</v>
-      </c>
-      <c r="J53" s="146">
-        <v>13.45</v>
-      </c>
-      <c r="K53" s="148">
-        <v>14.9</v>
-      </c>
-      <c r="L53" s="148">
-        <v>46.85</v>
-      </c>
-      <c r="M53" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N53" s="153"/>
-      <c r="O53" s="92"/>
-      <c r="P53" s="75"/>
-      <c r="Q53" s="75"/>
-      <c r="R53" s="75"/>
-      <c r="S53" s="75"/>
-      <c r="T53" s="75"/>
-      <c r="U53" s="75"/>
-      <c r="V53" s="75"/>
-      <c r="W53" s="75"/>
-      <c r="X53" s="75"/>
-      <c r="Y53" s="75"/>
-    </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A54" s="151"/>
-      <c r="B54" s="141">
-        <v>-8477</v>
-      </c>
-      <c r="C54" s="152"/>
-      <c r="D54" s="148">
-        <v>13</v>
-      </c>
-      <c r="E54" s="147">
-        <v>-1.11E-2</v>
-      </c>
-      <c r="F54" s="148">
-        <v>6</v>
-      </c>
-      <c r="G54" s="148">
-        <v>3</v>
-      </c>
-      <c r="H54" s="148">
-        <v>1</v>
-      </c>
-      <c r="I54" s="148">
-        <v>13.55</v>
-      </c>
-      <c r="J54" s="146">
-        <v>13.3</v>
-      </c>
-      <c r="K54" s="148">
-        <v>12.2</v>
-      </c>
-      <c r="L54" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M54" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N54" s="153"/>
-      <c r="O54" s="92"/>
-      <c r="P54" s="75"/>
-      <c r="Q54" s="75"/>
-      <c r="R54" s="75"/>
-      <c r="S54" s="75"/>
-      <c r="T54" s="75"/>
-      <c r="U54" s="75"/>
-      <c r="V54" s="75"/>
-      <c r="W54" s="75"/>
-      <c r="X54" s="75"/>
-      <c r="Y54" s="75"/>
-    </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A55" s="151"/>
-      <c r="B55" s="141" t="s">
-        <v>11</v>
-      </c>
-      <c r="C55" s="152">
-        <v>0.5625</v>
-      </c>
-      <c r="D55" s="146">
-        <v>48.3</v>
-      </c>
-      <c r="E55" s="146">
-        <v>-0.3</v>
-      </c>
-      <c r="F55" s="146">
-        <v>48.25</v>
-      </c>
-      <c r="G55" s="146">
-        <v>48.3</v>
-      </c>
-      <c r="H55" s="148">
-        <v>61</v>
-      </c>
-      <c r="I55" s="142">
-        <v>48.65</v>
-      </c>
-      <c r="J55" s="142">
-        <v>48.65</v>
-      </c>
-      <c r="K55" s="148">
-        <v>53.4</v>
-      </c>
-      <c r="L55" s="148">
-        <v>49.25</v>
-      </c>
-      <c r="M55" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N55" s="153"/>
-      <c r="O55" s="92"/>
-      <c r="P55" s="75"/>
-      <c r="Q55" s="75"/>
-      <c r="R55" s="75"/>
-      <c r="S55" s="75"/>
-      <c r="T55" s="75"/>
-      <c r="U55" s="75"/>
-      <c r="V55" s="75"/>
-      <c r="W55" s="75"/>
-      <c r="X55" s="75"/>
-      <c r="Y55" s="75"/>
-    </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A56" s="151"/>
-      <c r="B56" s="141">
-        <v>-2739</v>
-      </c>
-      <c r="C56" s="152"/>
-      <c r="D56" s="148">
-        <v>83</v>
-      </c>
-      <c r="E56" s="147">
-        <v>-6.1999999999999998E-3</v>
-      </c>
-      <c r="F56" s="148">
-        <v>1</v>
-      </c>
-      <c r="G56" s="148">
-        <v>1</v>
-      </c>
-      <c r="H56" s="148">
-        <v>22</v>
-      </c>
-      <c r="I56" s="148">
-        <v>48.6</v>
-      </c>
-      <c r="J56" s="146">
-        <v>48.05</v>
-      </c>
-      <c r="K56" s="148">
-        <v>43.75</v>
-      </c>
-      <c r="L56" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M56" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N56" s="153"/>
-      <c r="O56" s="92"/>
-      <c r="P56" s="75"/>
-      <c r="Q56" s="75"/>
-      <c r="R56" s="75"/>
-      <c r="S56" s="75"/>
-      <c r="T56" s="75"/>
-      <c r="U56" s="75"/>
-      <c r="V56" s="75"/>
-      <c r="W56" s="75"/>
-      <c r="X56" s="75"/>
-      <c r="Y56" s="75"/>
-    </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A57" s="151"/>
-      <c r="B57" s="141" t="s">
-        <v>12</v>
-      </c>
-      <c r="C57" s="152">
-        <v>0.5625</v>
-      </c>
-      <c r="D57" s="146">
-        <v>58.6</v>
-      </c>
-      <c r="E57" s="146">
-        <v>-0.5</v>
-      </c>
-      <c r="F57" s="146">
-        <v>58.6</v>
-      </c>
-      <c r="G57" s="146">
-        <v>58.7</v>
-      </c>
-      <c r="H57" s="148">
-        <v>77</v>
-      </c>
-      <c r="I57" s="142">
-        <v>60.2</v>
-      </c>
-      <c r="J57" s="142">
-        <v>60.2</v>
-      </c>
-      <c r="K57" s="148">
-        <v>65</v>
-      </c>
-      <c r="L57" s="148">
-        <v>53.9</v>
-      </c>
-      <c r="M57" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N57" s="153"/>
-      <c r="O57" s="92"/>
-      <c r="P57" s="75"/>
-      <c r="Q57" s="75"/>
-      <c r="R57" s="75"/>
-      <c r="S57" s="75"/>
-      <c r="T57" s="75"/>
-      <c r="U57" s="75"/>
-      <c r="V57" s="75"/>
-      <c r="W57" s="75"/>
-      <c r="X57" s="75"/>
-      <c r="Y57" s="75"/>
-    </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A58" s="151"/>
-      <c r="B58" s="141">
-        <v>-2748</v>
-      </c>
-      <c r="C58" s="152"/>
-      <c r="D58" s="148">
-        <v>118</v>
-      </c>
-      <c r="E58" s="147">
-        <v>-8.5000000000000006E-3</v>
-      </c>
-      <c r="F58" s="148">
-        <v>2</v>
-      </c>
-      <c r="G58" s="148">
-        <v>1</v>
-      </c>
-      <c r="H58" s="148">
-        <v>40</v>
-      </c>
-      <c r="I58" s="148">
-        <v>59.1</v>
-      </c>
-      <c r="J58" s="146">
-        <v>58.5</v>
-      </c>
-      <c r="K58" s="148">
-        <v>53.2</v>
-      </c>
-      <c r="L58" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M58" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N58" s="153"/>
-      <c r="O58" s="92"/>
-      <c r="P58" s="75"/>
-      <c r="Q58" s="75"/>
-      <c r="R58" s="75"/>
-      <c r="S58" s="75"/>
-      <c r="T58" s="75"/>
-      <c r="U58" s="75"/>
-      <c r="V58" s="75"/>
-      <c r="W58" s="75"/>
-      <c r="X58" s="75"/>
-      <c r="Y58" s="75"/>
-    </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A59" s="151"/>
-      <c r="B59" s="141" t="s">
-        <v>13</v>
-      </c>
-      <c r="C59" s="152">
-        <v>0.5625</v>
-      </c>
-      <c r="D59" s="148">
-        <v>52</v>
-      </c>
-      <c r="E59" s="148" t="s">
-        <v>14</v>
-      </c>
-      <c r="F59" s="148">
-        <v>52</v>
-      </c>
-      <c r="G59" s="142">
-        <v>52.1</v>
-      </c>
-      <c r="H59" s="148">
-        <v>4</v>
-      </c>
-      <c r="I59" s="142">
-        <v>52.4</v>
-      </c>
-      <c r="J59" s="142">
-        <v>52.4</v>
-      </c>
-      <c r="K59" s="148">
-        <v>57.2</v>
-      </c>
-      <c r="L59" s="148">
-        <v>188.5</v>
-      </c>
-      <c r="M59" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N59" s="153"/>
-      <c r="O59" s="92"/>
-      <c r="P59" s="75"/>
-      <c r="Q59" s="75"/>
-      <c r="R59" s="75"/>
-      <c r="S59" s="75"/>
-      <c r="T59" s="75"/>
-      <c r="U59" s="75"/>
-      <c r="V59" s="75"/>
-      <c r="W59" s="75"/>
-      <c r="X59" s="75"/>
-      <c r="Y59" s="75"/>
-    </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A60" s="151"/>
-      <c r="B60" s="141">
-        <v>-2926</v>
-      </c>
-      <c r="C60" s="152"/>
-      <c r="D60" s="148">
-        <v>9</v>
-      </c>
-      <c r="E60" s="148" t="s">
-        <v>14</v>
-      </c>
-      <c r="F60" s="148">
-        <v>1</v>
-      </c>
-      <c r="G60" s="148">
-        <v>1</v>
-      </c>
-      <c r="H60" s="148">
-        <v>5</v>
-      </c>
-      <c r="I60" s="148">
-        <v>52</v>
-      </c>
-      <c r="J60" s="146">
-        <v>51.6</v>
-      </c>
-      <c r="K60" s="148">
-        <v>46.8</v>
-      </c>
-      <c r="L60" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M60" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N60" s="153"/>
-      <c r="O60" s="92"/>
-      <c r="P60" s="75"/>
-      <c r="Q60" s="75"/>
-      <c r="R60" s="75"/>
-      <c r="S60" s="75"/>
-      <c r="T60" s="75"/>
-      <c r="U60" s="75"/>
-      <c r="V60" s="75"/>
-      <c r="W60" s="75"/>
-      <c r="X60" s="75"/>
-      <c r="Y60" s="75"/>
-    </row>
-    <row r="61" spans="1:25" s="75" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="151"/>
-      <c r="B61" s="141" t="s">
-        <v>15</v>
-      </c>
-      <c r="C61" s="152">
-        <v>0.58262731481481478</v>
-      </c>
-      <c r="D61" s="146">
-        <v>34.950000000000003</v>
-      </c>
-      <c r="E61" s="146">
-        <v>-0.22</v>
-      </c>
-      <c r="F61" s="146">
-        <v>33.299999999999997</v>
-      </c>
-      <c r="G61" s="146">
-        <v>34.950000000000003</v>
-      </c>
-      <c r="H61" s="148">
-        <v>7</v>
-      </c>
-      <c r="I61" s="146">
-        <v>34.9</v>
-      </c>
-      <c r="J61" s="146">
-        <v>35</v>
-      </c>
-      <c r="K61" s="148" t="s">
-        <v>14</v>
-      </c>
-      <c r="L61" s="148">
-        <v>49</v>
-      </c>
-      <c r="M61" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N61" s="153"/>
-      <c r="O61" s="92"/>
-    </row>
-    <row r="62" spans="1:25" s="75" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="151"/>
-      <c r="B62" s="141">
-        <v>-2942</v>
-      </c>
-      <c r="C62" s="152"/>
-      <c r="D62" s="148">
-        <v>12</v>
-      </c>
-      <c r="E62" s="147">
-        <v>-6.3E-3</v>
-      </c>
-      <c r="F62" s="145">
-        <v>3000</v>
-      </c>
-      <c r="G62" s="145">
-        <v>1986</v>
-      </c>
-      <c r="H62" s="148">
-        <v>4</v>
-      </c>
-      <c r="I62" s="142">
-        <v>35.17</v>
-      </c>
-      <c r="J62" s="146">
-        <v>34.85</v>
-      </c>
-      <c r="K62" s="148" t="s">
-        <v>14</v>
-      </c>
-      <c r="L62" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M62" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N62" s="153"/>
-      <c r="O62" s="92"/>
-    </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A63" s="151"/>
-      <c r="B63" s="141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" s="152">
-        <v>0.5625</v>
-      </c>
-      <c r="D63" s="146">
-        <v>257</v>
-      </c>
-      <c r="E63" s="146">
-        <v>-0.5</v>
-      </c>
-      <c r="F63" s="146">
-        <v>257</v>
-      </c>
-      <c r="G63" s="148">
-        <v>257.5</v>
-      </c>
-      <c r="H63" s="148">
-        <v>919</v>
-      </c>
-      <c r="I63" s="142">
-        <v>259</v>
-      </c>
-      <c r="J63" s="142">
-        <v>259.5</v>
-      </c>
-      <c r="K63" s="148">
-        <v>283</v>
-      </c>
-      <c r="L63" s="148">
-        <v>210</v>
-      </c>
-      <c r="M63" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N63" s="153"/>
-      <c r="O63" s="92"/>
-      <c r="P63" s="75"/>
-      <c r="Q63" s="75"/>
-      <c r="R63" s="75"/>
-      <c r="S63" s="75"/>
-      <c r="T63" s="75"/>
-      <c r="U63" s="75"/>
-      <c r="V63" s="75"/>
-      <c r="W63" s="75"/>
-      <c r="X63" s="75"/>
-      <c r="Y63" s="75"/>
-    </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A64" s="151"/>
-      <c r="B64" s="141">
-        <v>-2912</v>
-      </c>
-      <c r="C64" s="152"/>
-      <c r="D64" s="145">
-        <v>1218</v>
-      </c>
-      <c r="E64" s="147">
-        <v>-1.9E-3</v>
-      </c>
-      <c r="F64" s="148">
-        <v>329</v>
-      </c>
-      <c r="G64" s="148">
-        <v>1</v>
-      </c>
-      <c r="H64" s="148">
-        <v>271</v>
-      </c>
-      <c r="I64" s="148">
-        <v>257.5</v>
-      </c>
-      <c r="J64" s="146">
-        <v>257</v>
-      </c>
-      <c r="K64" s="148">
-        <v>232</v>
-      </c>
-      <c r="L64" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M64" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N64" s="153"/>
-      <c r="O64" s="92"/>
-      <c r="P64" s="75"/>
-      <c r="Q64" s="75"/>
-      <c r="R64" s="75"/>
-      <c r="S64" s="75"/>
-      <c r="T64" s="75"/>
-      <c r="U64" s="75"/>
-      <c r="V64" s="75"/>
-      <c r="W64" s="75"/>
-      <c r="X64" s="75"/>
-      <c r="Y64" s="75"/>
-    </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A65" s="151"/>
-      <c r="B65" s="141" t="s">
-        <v>17</v>
-      </c>
-      <c r="C65" s="152">
-        <v>0.5625</v>
-      </c>
-      <c r="D65" s="146">
-        <v>25.35</v>
-      </c>
-      <c r="E65" s="146">
-        <v>-0.05</v>
-      </c>
-      <c r="F65" s="146">
-        <v>25.3</v>
-      </c>
-      <c r="G65" s="146">
-        <v>25.35</v>
-      </c>
-      <c r="H65" s="145">
-        <v>1081</v>
-      </c>
-      <c r="I65" s="148">
-        <v>25.4</v>
-      </c>
-      <c r="J65" s="142">
-        <v>25.7</v>
-      </c>
-      <c r="K65" s="148">
-        <v>27.9</v>
-      </c>
-      <c r="L65" s="148">
-        <v>15.7</v>
-      </c>
-      <c r="M65" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N65" s="153"/>
-      <c r="O65" s="92"/>
-      <c r="P65" s="75"/>
-      <c r="Q65" s="75"/>
-      <c r="R65" s="75"/>
-      <c r="S65" s="75"/>
-      <c r="T65" s="75"/>
-      <c r="U65" s="75"/>
-      <c r="V65" s="75"/>
-      <c r="W65" s="75"/>
-      <c r="X65" s="75"/>
-      <c r="Y65" s="75"/>
-    </row>
-    <row r="66" spans="1:25" s="75" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="151"/>
-      <c r="B66" s="141">
-        <v>-2903</v>
-      </c>
-      <c r="C66" s="152"/>
-      <c r="D66" s="145">
-        <v>1803</v>
-      </c>
-      <c r="E66" s="147">
-        <v>-2E-3</v>
-      </c>
-      <c r="F66" s="148">
-        <v>66</v>
-      </c>
-      <c r="G66" s="148">
-        <v>12</v>
-      </c>
-      <c r="H66" s="148">
-        <v>720</v>
-      </c>
-      <c r="I66" s="148">
-        <v>25.4</v>
-      </c>
-      <c r="J66" s="146">
-        <v>25.15</v>
-      </c>
-      <c r="K66" s="148">
-        <v>22.9</v>
-      </c>
-      <c r="L66" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M66" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N66" s="153"/>
-      <c r="O66" s="92"/>
-    </row>
-    <row r="67" spans="1:25" s="75" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="151"/>
-      <c r="B67" s="141" t="s">
-        <v>18</v>
-      </c>
-      <c r="C67" s="152">
-        <v>0.5625</v>
-      </c>
-      <c r="D67" s="146">
-        <v>489.5</v>
-      </c>
-      <c r="E67" s="146">
-        <v>-5.5</v>
-      </c>
-      <c r="F67" s="146">
-        <v>489.5</v>
-      </c>
-      <c r="G67" s="146">
-        <v>492</v>
-      </c>
-      <c r="H67" s="148">
-        <v>183</v>
-      </c>
-      <c r="I67" s="142">
-        <v>496.5</v>
-      </c>
-      <c r="J67" s="142">
-        <v>500</v>
-      </c>
-      <c r="K67" s="148">
-        <v>544</v>
-      </c>
-      <c r="L67" s="148">
-        <v>339</v>
-      </c>
-      <c r="M67" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N67" s="153"/>
-      <c r="O67" s="92"/>
-    </row>
-    <row r="68" spans="1:25" s="75" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="151"/>
-      <c r="B68" s="141">
-        <v>-5904</v>
-      </c>
-      <c r="C68" s="152"/>
-      <c r="D68" s="148">
-        <v>298</v>
-      </c>
-      <c r="E68" s="147">
-        <v>-1.11E-2</v>
-      </c>
-      <c r="F68" s="148">
-        <v>1</v>
-      </c>
-      <c r="G68" s="148">
-        <v>1</v>
-      </c>
-      <c r="H68" s="148">
-        <v>114</v>
-      </c>
-      <c r="I68" s="148">
-        <v>495</v>
-      </c>
-      <c r="J68" s="146">
-        <v>489.5</v>
-      </c>
-      <c r="K68" s="148">
-        <v>445.5</v>
-      </c>
-      <c r="L68" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M68" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N68" s="153"/>
-      <c r="O68" s="92"/>
-    </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A69" s="151"/>
-      <c r="B69" s="141" t="s">
-        <v>19</v>
-      </c>
-      <c r="C69" s="152">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D69" s="146">
-        <v>9.61</v>
-      </c>
-      <c r="E69" s="146">
-        <v>-0.25</v>
-      </c>
-      <c r="F69" s="146">
-        <v>9.61</v>
-      </c>
-      <c r="G69" s="146">
-        <v>9.6199999999999992</v>
-      </c>
-      <c r="H69" s="148">
-        <v>415</v>
-      </c>
-      <c r="I69" s="142">
-        <v>9.8800000000000008</v>
-      </c>
-      <c r="J69" s="142">
-        <v>9.9</v>
-      </c>
-      <c r="K69" s="148">
-        <v>10.8</v>
-      </c>
-      <c r="L69" s="148">
-        <v>32.35</v>
-      </c>
-      <c r="M69" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N69" s="153"/>
-      <c r="O69" s="92"/>
-      <c r="P69" s="75"/>
-      <c r="Q69" s="75"/>
-      <c r="R69" s="75"/>
-      <c r="S69" s="75"/>
-      <c r="T69" s="75"/>
-      <c r="U69" s="75"/>
-      <c r="V69" s="75"/>
-      <c r="W69" s="75"/>
-      <c r="X69" s="75"/>
-      <c r="Y69" s="75"/>
-    </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A70" s="151"/>
-      <c r="B70" s="141">
-        <v>-5907</v>
-      </c>
-      <c r="C70" s="152"/>
-      <c r="D70" s="148">
-        <v>561</v>
-      </c>
-      <c r="E70" s="147">
-        <v>-2.5399999999999999E-2</v>
-      </c>
-      <c r="F70" s="148">
-        <v>1</v>
-      </c>
-      <c r="G70" s="148">
-        <v>2</v>
-      </c>
-      <c r="H70" s="148">
-        <v>146</v>
-      </c>
-      <c r="I70" s="148">
-        <v>9.86</v>
-      </c>
-      <c r="J70" s="146">
-        <v>9.59</v>
-      </c>
-      <c r="K70" s="148">
-        <v>8.8800000000000008</v>
-      </c>
-      <c r="L70" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M70" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N70" s="153"/>
-      <c r="O70" s="92"/>
-      <c r="P70" s="75"/>
-      <c r="Q70" s="75"/>
-      <c r="R70" s="75"/>
-      <c r="S70" s="75"/>
-      <c r="T70" s="75"/>
-      <c r="U70" s="75"/>
-      <c r="V70" s="75"/>
-      <c r="W70" s="75"/>
-      <c r="X70" s="75"/>
-      <c r="Y70" s="75"/>
-    </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A71" s="151"/>
-      <c r="B71" s="141" t="s">
-        <v>20</v>
-      </c>
-      <c r="C71" s="152">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D71" s="142">
-        <v>216.5</v>
-      </c>
-      <c r="E71" s="142">
-        <v>3</v>
-      </c>
-      <c r="F71" s="142">
-        <v>216.5</v>
-      </c>
-      <c r="G71" s="142">
-        <v>217</v>
-      </c>
-      <c r="H71" s="148">
-        <v>142</v>
-      </c>
-      <c r="I71" s="142">
-        <v>215</v>
-      </c>
-      <c r="J71" s="142">
-        <v>217</v>
-      </c>
-      <c r="K71" s="148">
-        <v>234.5</v>
-      </c>
-      <c r="L71" s="148">
-        <v>219</v>
-      </c>
-      <c r="M71" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N71" s="153"/>
-      <c r="O71" s="92"/>
-      <c r="P71" s="75"/>
-      <c r="Q71" s="75"/>
-      <c r="R71" s="75"/>
-      <c r="S71" s="75"/>
-      <c r="T71" s="75"/>
-      <c r="U71" s="75"/>
-      <c r="V71" s="75"/>
-      <c r="W71" s="75"/>
-      <c r="X71" s="75"/>
-      <c r="Y71" s="75"/>
-    </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A72" s="151"/>
-      <c r="B72" s="141">
-        <v>-2707</v>
-      </c>
-      <c r="C72" s="152"/>
-      <c r="D72" s="148">
-        <v>679</v>
-      </c>
-      <c r="E72" s="144">
-        <v>1.41E-2</v>
-      </c>
-      <c r="F72" s="148">
-        <v>1</v>
-      </c>
-      <c r="G72" s="148">
-        <v>48</v>
-      </c>
-      <c r="H72" s="148">
-        <v>532</v>
-      </c>
-      <c r="I72" s="148">
-        <v>213.5</v>
-      </c>
-      <c r="J72" s="146">
-        <v>212</v>
-      </c>
-      <c r="K72" s="148">
-        <v>192.5</v>
-      </c>
-      <c r="L72" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M72" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N72" s="153"/>
-      <c r="O72" s="92"/>
-      <c r="P72" s="75"/>
-      <c r="Q72" s="75"/>
-      <c r="R72" s="75"/>
-      <c r="S72" s="75"/>
-      <c r="T72" s="75"/>
-      <c r="U72" s="75"/>
-      <c r="V72" s="75"/>
-      <c r="W72" s="75"/>
-      <c r="X72" s="75"/>
-      <c r="Y72" s="75"/>
-    </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A73" s="151"/>
-      <c r="B73" s="141" t="s">
-        <v>21</v>
-      </c>
-      <c r="C73" s="152">
-        <v>0.5625</v>
-      </c>
-      <c r="D73" s="148">
-        <v>51.4</v>
-      </c>
-      <c r="E73" s="148" t="s">
-        <v>14</v>
-      </c>
-      <c r="F73" s="148">
-        <v>51.4</v>
-      </c>
-      <c r="G73" s="142">
-        <v>51.5</v>
-      </c>
-      <c r="H73" s="148">
-        <v>45</v>
-      </c>
-      <c r="I73" s="146">
-        <v>51.2</v>
-      </c>
-      <c r="J73" s="142">
-        <v>51.6</v>
-      </c>
-      <c r="K73" s="148">
-        <v>56.5</v>
-      </c>
-      <c r="L73" s="148">
-        <v>25.4</v>
-      </c>
-      <c r="M73" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N73" s="153"/>
-      <c r="O73" s="92"/>
-      <c r="P73" s="75"/>
-      <c r="Q73" s="75"/>
-      <c r="R73" s="75"/>
-      <c r="S73" s="75"/>
-      <c r="T73" s="75"/>
-      <c r="U73" s="75"/>
-      <c r="V73" s="75"/>
-      <c r="W73" s="75"/>
-      <c r="X73" s="75"/>
-      <c r="Y73" s="75"/>
-    </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A74" s="151"/>
-      <c r="B74" s="141">
-        <v>-2704</v>
-      </c>
-      <c r="C74" s="152"/>
-      <c r="D74" s="148">
-        <v>60</v>
-      </c>
-      <c r="E74" s="148" t="s">
-        <v>14</v>
-      </c>
-      <c r="F74" s="148">
-        <v>3</v>
-      </c>
-      <c r="G74" s="148">
-        <v>1</v>
-      </c>
-      <c r="H74" s="148">
-        <v>5</v>
-      </c>
-      <c r="I74" s="148">
-        <v>51.4</v>
-      </c>
-      <c r="J74" s="146">
-        <v>51.2</v>
-      </c>
-      <c r="K74" s="148">
-        <v>46.3</v>
-      </c>
-      <c r="L74" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M74" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N74" s="153"/>
-      <c r="O74" s="92"/>
-      <c r="P74" s="75"/>
-      <c r="Q74" s="75"/>
-      <c r="R74" s="75"/>
-      <c r="S74" s="75"/>
-      <c r="T74" s="75"/>
-      <c r="U74" s="75"/>
-      <c r="V74" s="75"/>
-      <c r="W74" s="75"/>
-      <c r="X74" s="75"/>
-      <c r="Y74" s="75"/>
-    </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A75" s="151"/>
-      <c r="B75" s="141" t="s">
-        <v>22</v>
-      </c>
-      <c r="C75" s="152">
-        <v>0.5625</v>
-      </c>
-      <c r="D75" s="146">
-        <v>96</v>
-      </c>
-      <c r="E75" s="146">
-        <v>-0.5</v>
-      </c>
-      <c r="F75" s="146">
-        <v>95.6</v>
-      </c>
-      <c r="G75" s="146">
-        <v>96</v>
-      </c>
-      <c r="H75" s="148">
-        <v>142</v>
-      </c>
-      <c r="I75" s="148">
-        <v>96.5</v>
-      </c>
-      <c r="J75" s="148">
-        <v>96.5</v>
-      </c>
-      <c r="K75" s="148">
-        <v>106</v>
-      </c>
-      <c r="L75" s="148">
-        <v>167</v>
-      </c>
-      <c r="M75" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N75" s="154"/>
-      <c r="O75" s="92"/>
-      <c r="P75" s="75"/>
-      <c r="Q75" s="75"/>
-      <c r="R75" s="75"/>
-      <c r="S75" s="75"/>
-      <c r="T75" s="75"/>
-      <c r="U75" s="75"/>
-      <c r="V75" s="75"/>
-      <c r="W75" s="75"/>
-      <c r="X75" s="75"/>
-      <c r="Y75" s="75"/>
-    </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A76" s="151"/>
-      <c r="B76" s="141">
-        <v>-2723</v>
-      </c>
-      <c r="C76" s="152"/>
-      <c r="D76" s="148">
-        <v>207</v>
-      </c>
-      <c r="E76" s="147">
-        <v>-5.1999999999999998E-3</v>
-      </c>
-      <c r="F76" s="148">
-        <v>3</v>
-      </c>
-      <c r="G76" s="148">
-        <v>5</v>
-      </c>
-      <c r="H76" s="148">
-        <v>65</v>
-      </c>
-      <c r="I76" s="148">
-        <v>96.5</v>
-      </c>
-      <c r="J76" s="146">
-        <v>95.5</v>
-      </c>
-      <c r="K76" s="148">
-        <v>86.9</v>
-      </c>
-      <c r="L76" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M76" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N76" s="154"/>
-      <c r="O76" s="89"/>
-      <c r="P76" s="75"/>
-      <c r="Q76" s="75"/>
-      <c r="R76" s="75"/>
-      <c r="S76" s="75"/>
-      <c r="T76" s="75"/>
-      <c r="U76" s="75"/>
-      <c r="V76" s="75"/>
-      <c r="W76" s="75"/>
-      <c r="X76" s="75"/>
-      <c r="Y76" s="75"/>
-    </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A77" s="151"/>
-      <c r="B77" s="141" t="s">
-        <v>23</v>
-      </c>
-      <c r="C77" s="152">
-        <v>0.5625</v>
-      </c>
-      <c r="D77" s="146">
-        <v>232.5</v>
-      </c>
-      <c r="E77" s="146">
-        <v>-0.5</v>
-      </c>
-      <c r="F77" s="146">
-        <v>232</v>
-      </c>
-      <c r="G77" s="148">
-        <v>233</v>
-      </c>
-      <c r="H77" s="148">
-        <v>174</v>
-      </c>
-      <c r="I77" s="142">
-        <v>233.5</v>
-      </c>
-      <c r="J77" s="142">
-        <v>233.5</v>
-      </c>
-      <c r="K77" s="148">
-        <v>256</v>
-      </c>
-      <c r="L77" s="148">
-        <v>181.5</v>
-      </c>
-      <c r="M77" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N77" s="155"/>
-      <c r="O77" s="89"/>
-      <c r="P77" s="75"/>
-      <c r="Q77" s="75"/>
-      <c r="R77" s="75"/>
-      <c r="S77" s="75"/>
-      <c r="T77" s="75"/>
-      <c r="U77" s="75"/>
-      <c r="V77" s="75"/>
-      <c r="W77" s="75"/>
-      <c r="X77" s="75"/>
-      <c r="Y77" s="75"/>
-    </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A78" s="151"/>
-      <c r="B78" s="141">
-        <v>-2727</v>
-      </c>
-      <c r="C78" s="152"/>
-      <c r="D78" s="148">
-        <v>256</v>
-      </c>
-      <c r="E78" s="147">
-        <v>-2.0999999999999999E-3</v>
-      </c>
-      <c r="F78" s="148">
-        <v>5</v>
-      </c>
-      <c r="G78" s="148">
-        <v>10</v>
-      </c>
-      <c r="H78" s="148">
-        <v>80</v>
-      </c>
-      <c r="I78" s="148">
-        <v>233</v>
-      </c>
-      <c r="J78" s="146">
-        <v>231</v>
-      </c>
-      <c r="K78" s="148">
-        <v>210</v>
-      </c>
-      <c r="L78" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M78" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N78" s="155"/>
-      <c r="O78" s="89"/>
-      <c r="P78" s="75"/>
-      <c r="Q78" s="75"/>
-      <c r="R78" s="75"/>
-      <c r="S78" s="75"/>
-      <c r="T78" s="75"/>
-      <c r="U78" s="75"/>
-      <c r="V78" s="75"/>
-      <c r="W78" s="75"/>
-      <c r="X78" s="75"/>
-      <c r="Y78" s="75"/>
-    </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A79" s="151"/>
-      <c r="B79" s="141" t="s">
-        <v>24</v>
-      </c>
-      <c r="C79" s="152">
-        <v>0.62443287037037043</v>
-      </c>
-      <c r="D79" s="148" t="s">
-        <v>14</v>
-      </c>
-      <c r="E79" s="148" t="s">
-        <v>14</v>
-      </c>
-      <c r="F79" s="146">
-        <v>63</v>
-      </c>
-      <c r="G79" s="146">
-        <v>64.400000000000006</v>
-      </c>
-      <c r="H79" s="148" t="s">
-        <v>14</v>
-      </c>
-      <c r="I79" s="148" t="s">
-        <v>14</v>
-      </c>
-      <c r="J79" s="148" t="s">
-        <v>14</v>
-      </c>
-      <c r="K79" s="148">
-        <v>71.099999999999994</v>
-      </c>
-      <c r="L79" s="148">
-        <v>63.4</v>
-      </c>
-      <c r="M79" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N79" s="155"/>
-      <c r="O79" s="89"/>
-      <c r="P79" s="75"/>
-      <c r="Q79" s="75"/>
-      <c r="R79" s="75"/>
-      <c r="S79" s="75"/>
-      <c r="T79" s="75"/>
-      <c r="U79" s="75"/>
-      <c r="V79" s="75"/>
-      <c r="W79" s="75"/>
-      <c r="X79" s="75"/>
-      <c r="Y79" s="75"/>
-    </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A80" s="151"/>
-      <c r="B80" s="141">
-        <v>-1259</v>
-      </c>
-      <c r="C80" s="152"/>
-      <c r="D80" s="148" t="s">
-        <v>14</v>
-      </c>
-      <c r="E80" s="148" t="s">
-        <v>14</v>
-      </c>
-      <c r="F80" s="148">
-        <v>2</v>
-      </c>
-      <c r="G80" s="148">
-        <v>1</v>
-      </c>
-      <c r="H80" s="148" t="s">
-        <v>14</v>
-      </c>
-      <c r="I80" s="148">
-        <v>64.7</v>
-      </c>
-      <c r="J80" s="148" t="s">
-        <v>14</v>
-      </c>
-      <c r="K80" s="148">
-        <v>58.3</v>
-      </c>
-      <c r="L80" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M80" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N80" s="155"/>
-      <c r="O80" s="89"/>
-      <c r="P80" s="75"/>
-      <c r="Q80" s="75"/>
-      <c r="R80" s="75"/>
-      <c r="S80" s="75"/>
-      <c r="T80" s="75"/>
-      <c r="U80" s="75"/>
-      <c r="V80" s="75"/>
-      <c r="W80" s="75"/>
-      <c r="X80" s="75"/>
-      <c r="Y80" s="75"/>
-    </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A81" s="151"/>
-      <c r="B81" s="141" t="s">
-        <v>7</v>
-      </c>
-      <c r="C81" s="152">
-        <v>0.55621527777777779</v>
-      </c>
-      <c r="D81" s="142">
-        <v>200.5</v>
-      </c>
-      <c r="E81" s="142">
-        <v>0.5</v>
-      </c>
-      <c r="F81" s="146">
-        <v>199</v>
-      </c>
-      <c r="G81" s="148">
-        <v>200</v>
-      </c>
-      <c r="H81" s="148">
-        <v>6</v>
-      </c>
-      <c r="I81" s="146">
-        <v>199</v>
-      </c>
-      <c r="J81" s="142">
-        <v>200.5</v>
-      </c>
-      <c r="K81" s="148">
-        <v>220</v>
-      </c>
-      <c r="L81" s="148">
-        <v>232</v>
-      </c>
-      <c r="M81" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N81" s="155"/>
-      <c r="O81" s="89"/>
-      <c r="P81" s="75"/>
-      <c r="Q81" s="75"/>
-      <c r="R81" s="75"/>
-      <c r="S81" s="75"/>
-      <c r="T81" s="75"/>
-      <c r="U81" s="75"/>
-      <c r="V81" s="75"/>
-      <c r="W81" s="75"/>
-      <c r="X81" s="75"/>
-      <c r="Y81" s="75"/>
-    </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A82" s="151"/>
-      <c r="B82" s="141">
-        <v>-2729</v>
-      </c>
-      <c r="C82" s="152"/>
-      <c r="D82" s="148">
-        <v>13</v>
-      </c>
-      <c r="E82" s="144">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="F82" s="148">
-        <v>2</v>
-      </c>
-      <c r="G82" s="148">
-        <v>2</v>
-      </c>
-      <c r="H82" s="148">
-        <v>7</v>
-      </c>
-      <c r="I82" s="148">
-        <v>200</v>
-      </c>
-      <c r="J82" s="146">
-        <v>199</v>
-      </c>
-      <c r="K82" s="148">
-        <v>180</v>
-      </c>
-      <c r="L82" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M82" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N82" s="155"/>
-      <c r="O82" s="89"/>
-      <c r="P82" s="75"/>
-      <c r="Q82" s="75"/>
-      <c r="R82" s="75"/>
-      <c r="S82" s="75"/>
-      <c r="T82" s="75"/>
-      <c r="U82" s="75"/>
-      <c r="V82" s="75"/>
-      <c r="W82" s="75"/>
-      <c r="X82" s="75"/>
-      <c r="Y82" s="75"/>
-    </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A83" s="151"/>
-      <c r="B83" s="141" t="s">
-        <v>25</v>
-      </c>
-      <c r="C83" s="152">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D83" s="146">
-        <v>75.400000000000006</v>
-      </c>
-      <c r="E83" s="146">
-        <v>-0.2</v>
-      </c>
-      <c r="F83" s="146">
-        <v>75.2</v>
-      </c>
-      <c r="G83" s="146">
-        <v>75.400000000000006</v>
-      </c>
-      <c r="H83" s="145">
-        <v>1413</v>
-      </c>
-      <c r="I83" s="146">
-        <v>75.5</v>
-      </c>
-      <c r="J83" s="148">
-        <v>75.599999999999994</v>
-      </c>
-      <c r="K83" s="148">
-        <v>83.1</v>
-      </c>
-      <c r="L83" s="148">
-        <v>32.450000000000003</v>
-      </c>
-      <c r="M83" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N83" s="155"/>
-      <c r="O83" s="89"/>
-      <c r="P83" s="75"/>
-      <c r="Q83" s="75"/>
-      <c r="R83" s="75"/>
-      <c r="S83" s="75"/>
-      <c r="T83" s="75"/>
-      <c r="U83" s="75"/>
-      <c r="V83" s="75"/>
-      <c r="W83" s="75"/>
-      <c r="X83" s="75"/>
-      <c r="Y83" s="75"/>
-    </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A84" s="151"/>
-      <c r="B84" s="141">
-        <v>-2347</v>
-      </c>
-      <c r="C84" s="152"/>
-      <c r="D84" s="145">
-        <v>3669</v>
-      </c>
-      <c r="E84" s="147">
-        <v>-2.5999999999999999E-3</v>
-      </c>
-      <c r="F84" s="148">
-        <v>12</v>
-      </c>
-      <c r="G84" s="148">
-        <v>76</v>
-      </c>
-      <c r="H84" s="145">
-        <v>2240</v>
-      </c>
-      <c r="I84" s="148">
-        <v>75.599999999999994</v>
-      </c>
-      <c r="J84" s="146">
-        <v>74.400000000000006</v>
-      </c>
-      <c r="K84" s="148">
-        <v>68.099999999999994</v>
-      </c>
-      <c r="L84" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M84" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N84" s="155"/>
-      <c r="O84" s="89"/>
-      <c r="P84" s="75"/>
-      <c r="Q84" s="75"/>
-      <c r="R84" s="75"/>
-      <c r="S84" s="75"/>
-      <c r="T84" s="75"/>
-      <c r="U84" s="75"/>
-      <c r="V84" s="75"/>
-      <c r="W84" s="75"/>
-      <c r="X84" s="75"/>
-      <c r="Y84" s="75"/>
-    </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A85" s="151"/>
-      <c r="B85" s="141" t="s">
-        <v>26</v>
-      </c>
-      <c r="C85" s="152">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D85" s="146">
-        <v>50.5</v>
-      </c>
-      <c r="E85" s="146">
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="F85" s="146">
-        <v>50.4</v>
-      </c>
-      <c r="G85" s="146">
-        <v>50.6</v>
-      </c>
-      <c r="H85" s="148">
-        <v>860</v>
-      </c>
-      <c r="I85" s="142">
-        <v>52.2</v>
-      </c>
-      <c r="J85" s="142">
-        <v>52.2</v>
-      </c>
-      <c r="K85" s="148">
-        <v>56.7</v>
-      </c>
-      <c r="L85" s="148">
-        <v>30.3</v>
-      </c>
-      <c r="M85" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N85" s="155"/>
-      <c r="O85" s="89"/>
-      <c r="P85" s="75"/>
-      <c r="Q85" s="75"/>
-      <c r="R85" s="75"/>
-      <c r="S85" s="75"/>
-      <c r="T85" s="75"/>
-      <c r="U85" s="75"/>
-      <c r="V85" s="75"/>
-      <c r="W85" s="75"/>
-      <c r="X85" s="75"/>
-      <c r="Y85" s="75"/>
-    </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A86" s="151"/>
-      <c r="B86" s="141">
-        <v>-2362</v>
-      </c>
-      <c r="C86" s="152"/>
-      <c r="D86" s="145">
-        <v>1198</v>
-      </c>
-      <c r="E86" s="147">
-        <v>-2.1299999999999999E-2</v>
-      </c>
-      <c r="F86" s="148">
-        <v>13</v>
-      </c>
-      <c r="G86" s="148">
-        <v>5</v>
-      </c>
-      <c r="H86" s="148">
-        <v>332</v>
-      </c>
-      <c r="I86" s="148">
-        <v>51.6</v>
-      </c>
-      <c r="J86" s="146">
-        <v>50.2</v>
-      </c>
-      <c r="K86" s="148">
-        <v>46.45</v>
-      </c>
-      <c r="L86" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M86" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N86" s="155"/>
-      <c r="O86" s="89"/>
-      <c r="P86" s="75"/>
-      <c r="Q86" s="75"/>
-      <c r="R86" s="75"/>
-      <c r="S86" s="75"/>
-      <c r="T86" s="75"/>
-      <c r="U86" s="75"/>
-      <c r="V86" s="75"/>
-      <c r="W86" s="75"/>
-      <c r="X86" s="75"/>
-      <c r="Y86" s="75"/>
-    </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A87" s="151"/>
-      <c r="B87" s="141" t="s">
-        <v>27</v>
-      </c>
-      <c r="C87" s="152">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D87" s="146">
-        <v>42.2</v>
-      </c>
-      <c r="E87" s="146">
-        <v>-0.45</v>
-      </c>
-      <c r="F87" s="146">
-        <v>42.2</v>
-      </c>
-      <c r="G87" s="146">
-        <v>42.25</v>
-      </c>
-      <c r="H87" s="148">
-        <v>263</v>
-      </c>
-      <c r="I87" s="142">
-        <v>43.05</v>
-      </c>
-      <c r="J87" s="142">
-        <v>43.2</v>
-      </c>
-      <c r="K87" s="148">
-        <v>46.9</v>
-      </c>
-      <c r="L87" s="148">
-        <v>357</v>
-      </c>
-      <c r="M87" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N87" s="155"/>
-      <c r="O87" s="89"/>
-      <c r="P87" s="75"/>
-      <c r="Q87" s="75"/>
-      <c r="R87" s="75"/>
-      <c r="S87" s="75"/>
-      <c r="T87" s="75"/>
-      <c r="U87" s="75"/>
-      <c r="V87" s="75"/>
-      <c r="W87" s="75"/>
-      <c r="X87" s="75"/>
-      <c r="Y87" s="75"/>
-    </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A88" s="151"/>
-      <c r="B88" s="141">
-        <v>-8044</v>
-      </c>
-      <c r="C88" s="152"/>
-      <c r="D88" s="148">
-        <v>384</v>
-      </c>
-      <c r="E88" s="147">
-        <v>-1.06E-2</v>
-      </c>
-      <c r="F88" s="148">
-        <v>11</v>
-      </c>
-      <c r="G88" s="148">
-        <v>1</v>
-      </c>
-      <c r="H88" s="148">
-        <v>121</v>
-      </c>
-      <c r="I88" s="148">
-        <v>42.65</v>
-      </c>
-      <c r="J88" s="146">
-        <v>42.2</v>
-      </c>
-      <c r="K88" s="148">
-        <v>38.4</v>
-      </c>
-      <c r="L88" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M88" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N88" s="155"/>
-      <c r="O88" s="89"/>
-      <c r="P88" s="75"/>
-      <c r="Q88" s="75"/>
-      <c r="R88" s="75"/>
-      <c r="S88" s="75"/>
-      <c r="T88" s="75"/>
-      <c r="U88" s="75"/>
-      <c r="V88" s="75"/>
-      <c r="W88" s="75"/>
-      <c r="X88" s="75"/>
-      <c r="Y88" s="75"/>
-    </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A89" s="151"/>
-      <c r="B89" s="141" t="s">
-        <v>28</v>
-      </c>
-      <c r="C89" s="152">
-        <v>0.5625</v>
-      </c>
-      <c r="D89" s="146">
-        <v>362.5</v>
-      </c>
-      <c r="E89" s="146">
-        <v>-2.5</v>
-      </c>
-      <c r="F89" s="146">
-        <v>362</v>
-      </c>
-      <c r="G89" s="146">
-        <v>362.5</v>
-      </c>
-      <c r="H89" s="148">
-        <v>32</v>
-      </c>
-      <c r="I89" s="148">
-        <v>365</v>
-      </c>
-      <c r="J89" s="142">
-        <v>366</v>
-      </c>
-      <c r="K89" s="148">
-        <v>401.5</v>
-      </c>
-      <c r="L89" s="148">
-        <v>221</v>
-      </c>
-      <c r="M89" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N89" s="155"/>
-      <c r="O89" s="89"/>
-      <c r="P89" s="75"/>
-      <c r="Q89" s="75"/>
-      <c r="R89" s="75"/>
-      <c r="S89" s="75"/>
-      <c r="T89" s="75"/>
-      <c r="U89" s="75"/>
-      <c r="V89" s="75"/>
-      <c r="W89" s="75"/>
-      <c r="X89" s="75"/>
-      <c r="Y89" s="75"/>
-    </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A90" s="151"/>
-      <c r="B90" s="141">
-        <v>-8454</v>
-      </c>
-      <c r="C90" s="152"/>
-      <c r="D90" s="148">
-        <v>70</v>
-      </c>
-      <c r="E90" s="147">
-        <v>-6.7999999999999996E-3</v>
-      </c>
-      <c r="F90" s="148">
-        <v>6</v>
-      </c>
-      <c r="G90" s="148">
-        <v>1</v>
-      </c>
-      <c r="H90" s="148">
-        <v>37</v>
-      </c>
-      <c r="I90" s="148">
-        <v>365</v>
-      </c>
-      <c r="J90" s="146">
-        <v>361.5</v>
-      </c>
-      <c r="K90" s="148">
-        <v>328.5</v>
-      </c>
-      <c r="L90" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M90" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N90" s="155"/>
-      <c r="O90" s="89"/>
-      <c r="P90" s="75"/>
-      <c r="Q90" s="75"/>
-      <c r="R90" s="75"/>
-      <c r="S90" s="75"/>
-      <c r="T90" s="75"/>
-      <c r="U90" s="75"/>
-      <c r="V90" s="75"/>
-      <c r="W90" s="75"/>
-      <c r="X90" s="75"/>
-      <c r="Y90" s="75"/>
-    </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A91" s="151"/>
-      <c r="B91" s="141" t="s">
-        <v>139</v>
-      </c>
-      <c r="C91" s="152">
-        <v>0.5625</v>
-      </c>
-      <c r="D91" s="142">
-        <v>720</v>
-      </c>
-      <c r="E91" s="142">
-        <v>27</v>
-      </c>
-      <c r="F91" s="142">
-        <v>720</v>
-      </c>
-      <c r="G91" s="142">
-        <v>724</v>
-      </c>
-      <c r="H91" s="148">
-        <v>62</v>
-      </c>
-      <c r="I91" s="142">
-        <v>695</v>
-      </c>
-      <c r="J91" s="142">
-        <v>730</v>
-      </c>
-      <c r="K91" s="148">
-        <v>762</v>
-      </c>
-      <c r="L91" s="148">
-        <v>1030</v>
-      </c>
-      <c r="M91" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="N91" s="155"/>
-      <c r="O91" s="89"/>
-      <c r="P91" s="75"/>
-      <c r="Q91" s="75"/>
-      <c r="R91" s="75"/>
-      <c r="S91" s="75"/>
-      <c r="T91" s="75"/>
-      <c r="U91" s="75"/>
-      <c r="V91" s="75"/>
-      <c r="W91" s="75"/>
-      <c r="X91" s="75"/>
-      <c r="Y91" s="75"/>
-    </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A92" s="151"/>
-      <c r="B92" s="141">
-        <v>-7722</v>
-      </c>
-      <c r="C92" s="156"/>
-      <c r="D92" s="148">
-        <v>166</v>
-      </c>
-      <c r="E92" s="144">
-        <v>3.9E-2</v>
-      </c>
-      <c r="F92" s="148">
-        <v>5</v>
-      </c>
-      <c r="G92" s="148">
-        <v>1</v>
-      </c>
-      <c r="H92" s="148">
-        <v>104</v>
-      </c>
-      <c r="I92" s="148">
-        <v>693</v>
-      </c>
-      <c r="J92" s="146">
-        <v>692</v>
-      </c>
-      <c r="K92" s="148">
-        <v>624</v>
-      </c>
-      <c r="L92" s="148">
-        <v>1000</v>
-      </c>
-      <c r="M92" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="N92" s="155"/>
-      <c r="O92" s="89"/>
-      <c r="P92" s="75"/>
-      <c r="Q92" s="75"/>
-      <c r="R92" s="75"/>
-      <c r="S92" s="75"/>
-      <c r="T92" s="75"/>
-      <c r="U92" s="75"/>
-      <c r="V92" s="75"/>
-      <c r="W92" s="75"/>
-      <c r="X92" s="75"/>
-      <c r="Y92" s="75"/>
-    </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B93" s="79" t="s">
-        <v>9</v>
-      </c>
-      <c r="C93" s="79" t="s">
-        <v>96</v>
-      </c>
-      <c r="D93" s="79" t="s">
-        <v>29</v>
-      </c>
-      <c r="E93" s="79" t="s">
-        <v>30</v>
-      </c>
-      <c r="F93" s="79" t="s">
-        <v>31</v>
-      </c>
-      <c r="G93" s="79" t="s">
-        <v>32</v>
-      </c>
-      <c r="H93" s="79" t="s">
-        <v>33</v>
-      </c>
-      <c r="I93" s="79" t="s">
-        <v>34</v>
-      </c>
-      <c r="J93" s="79" t="s">
-        <v>35</v>
-      </c>
-      <c r="K93" s="79" t="s">
-        <v>6</v>
-      </c>
-      <c r="L93" s="79" t="s">
-        <v>36</v>
-      </c>
-      <c r="M93" s="79" t="s">
-        <v>37</v>
-      </c>
-      <c r="N93" s="80"/>
-      <c r="O93" s="89"/>
-      <c r="P93" s="75"/>
-      <c r="Q93" s="75"/>
-      <c r="R93" s="75"/>
-      <c r="S93" s="75"/>
-      <c r="T93" s="75"/>
-      <c r="U93" s="75"/>
-      <c r="V93" s="75"/>
-      <c r="W93" s="75"/>
-      <c r="X93" s="75"/>
-      <c r="Y93" s="75"/>
-    </row>
-    <row r="94" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="85" t="s">
-        <v>38</v>
-      </c>
-      <c r="B94" s="75" t="s">
-        <v>39</v>
-      </c>
-      <c r="C94" s="81">
-        <v>43091.666666666664</v>
-      </c>
-      <c r="D94" s="82"/>
-      <c r="E94" s="82"/>
-      <c r="F94" s="88">
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="G94" s="86">
-        <f>F94-M94</f>
-        <v>5.0000000000000044E-3</v>
-      </c>
-      <c r="H94" s="87">
-        <f>F94/M94-1</f>
-        <v>5.555555555555558E-2</v>
-      </c>
-      <c r="I94" s="98">
-        <v>1728</v>
-      </c>
-      <c r="J94" s="100">
-        <v>0.09</v>
-      </c>
-      <c r="K94" s="100">
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="L94" s="100">
-        <v>0.09</v>
-      </c>
-      <c r="M94" s="88">
-        <v>0.09</v>
-      </c>
-      <c r="N94" s="84"/>
-      <c r="O94" s="89"/>
-      <c r="P94" s="75"/>
-      <c r="Q94" s="75"/>
-      <c r="R94" s="75"/>
-      <c r="S94" s="75"/>
-      <c r="T94" s="75"/>
-      <c r="U94" s="75"/>
-      <c r="V94" s="75"/>
-      <c r="W94" s="75"/>
-      <c r="X94" s="75"/>
-      <c r="Y94" s="75"/>
-    </row>
-    <row r="95" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="85" t="s">
-        <v>40</v>
-      </c>
-      <c r="B95" s="75" t="s">
-        <v>41</v>
-      </c>
-      <c r="C95" s="81">
-        <v>43091.666666666664</v>
-      </c>
-      <c r="D95" s="83"/>
-      <c r="E95" s="82"/>
-      <c r="F95" s="88">
-        <v>0.315</v>
-      </c>
-      <c r="G95" s="86">
-        <f>F95-M95</f>
-        <v>0</v>
-      </c>
-      <c r="H95" s="87">
-        <f>F95/M95-1</f>
-        <v>0</v>
-      </c>
-      <c r="I95" s="98">
-        <v>47</v>
-      </c>
-      <c r="J95" s="100">
-        <v>0.32</v>
-      </c>
-      <c r="K95" s="100">
-        <v>0.32</v>
-      </c>
-      <c r="L95" s="100">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="M95" s="88">
-        <v>0.315</v>
-      </c>
-      <c r="N95" s="84"/>
-      <c r="O95" s="89"/>
-      <c r="P95" s="75"/>
-      <c r="Q95" s="75"/>
-      <c r="R95" s="75"/>
-      <c r="S95" s="75"/>
-      <c r="T95" s="75"/>
-      <c r="U95" s="75"/>
-      <c r="V95" s="75"/>
-      <c r="W95" s="75"/>
-      <c r="X95" s="75"/>
-      <c r="Y95" s="75"/>
-    </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B96" s="150"/>
-      <c r="C96" s="150"/>
-      <c r="D96" s="150"/>
-      <c r="E96" s="150"/>
-      <c r="F96" s="150"/>
-      <c r="G96" s="150"/>
-      <c r="H96" s="150"/>
-      <c r="I96" s="150"/>
-      <c r="J96" s="150"/>
-      <c r="K96" s="150"/>
-      <c r="L96" s="150"/>
-      <c r="M96" s="150"/>
-      <c r="N96" s="150"/>
-      <c r="O96" s="150"/>
-      <c r="P96" s="150"/>
-      <c r="Q96" s="75"/>
-      <c r="R96" s="75"/>
-      <c r="S96" s="75"/>
-      <c r="T96" s="75"/>
-      <c r="U96" s="75"/>
-      <c r="V96" s="75"/>
-      <c r="W96" s="75"/>
-      <c r="X96" s="75"/>
-      <c r="Y96" s="75"/>
-    </row>
   </sheetData>
   <dataConsolidate/>
-  <mergeCells count="74">
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="N91:N92"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="N87:N88"/>
-    <mergeCell ref="A89:A90"/>
-    <mergeCell ref="C89:C90"/>
-    <mergeCell ref="N89:N90"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="N83:N84"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="N85:N86"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="N79:N80"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="N81:N82"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="N75:N76"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="C77:C78"/>
-    <mergeCell ref="N77:N78"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="N71:N72"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="N73:N74"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="C67:C68"/>
-    <mergeCell ref="N67:N68"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="N69:N70"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="N63:N64"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="N65:N66"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="N59:N60"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="N61:N62"/>
-    <mergeCell ref="N53:N54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="N55:N56"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="N57:N58"/>
+  <mergeCells count="2">
     <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B96:P96"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="N45:N46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="N49:N50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="N51:N52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="B42:P42"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="O3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B45" r:id="rId2" display="https://pchome.megatime.com.tw/stock/sid2758.html" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B46" r:id="rId3" display="https://pchome.megatime.com.tw/stock/sid2758.html" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="B47" r:id="rId4" display="https://pchome.megatime.com.tw/stock/sid2945.html" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="B48" r:id="rId5" display="https://pchome.megatime.com.tw/stock/sid2945.html" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="B49" r:id="rId6" display="https://pchome.megatime.com.tw/stock/sid5903.html" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="B50" r:id="rId7" display="https://pchome.megatime.com.tw/stock/sid5903.html" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="B51" r:id="rId8" display="https://pchome.megatime.com.tw/stock/sid6741.html" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="B52" r:id="rId9" display="https://pchome.megatime.com.tw/stock/sid6741.html" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="B53" r:id="rId10" display="https://pchome.megatime.com.tw/stock/sid8477.html" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="B54" r:id="rId11" display="https://pchome.megatime.com.tw/stock/sid8477.html" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="B55" r:id="rId12" display="https://pchome.megatime.com.tw/stock/sid2739.html" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="B56" r:id="rId13" display="https://pchome.megatime.com.tw/stock/sid2739.html" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="B57" r:id="rId14" display="https://pchome.megatime.com.tw/stock/sid2748.html" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="B58" r:id="rId15" display="https://pchome.megatime.com.tw/stock/sid2748.html" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="B59" r:id="rId16" display="https://pchome.megatime.com.tw/stock/sid2926.html" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="B60" r:id="rId17" display="https://pchome.megatime.com.tw/stock/sid2926.html" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="B61" r:id="rId18" display="https://pchome.megatime.com.tw/stock/sid2942.html" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="B62" r:id="rId19" display="https://pchome.megatime.com.tw/stock/sid2942.html" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="B63" r:id="rId20" display="https://pchome.megatime.com.tw/stock/sid2912.html" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="B64" r:id="rId21" display="https://pchome.megatime.com.tw/stock/sid2912.html" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="B65" r:id="rId22" display="https://pchome.megatime.com.tw/stock/sid2903.html" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="B66" r:id="rId23" display="https://pchome.megatime.com.tw/stock/sid2903.html" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="B67" r:id="rId24" display="https://pchome.megatime.com.tw/stock/sid5904.html" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="B68" r:id="rId25" display="https://pchome.megatime.com.tw/stock/sid5904.html" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="B69" r:id="rId26" display="https://pchome.megatime.com.tw/stock/sid5907.html" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="B70" r:id="rId27" display="https://pchome.megatime.com.tw/stock/sid5907.html" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="B71" r:id="rId28" display="https://pchome.megatime.com.tw/stock/sid2707.html" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="B72" r:id="rId29" display="https://pchome.megatime.com.tw/stock/sid2707.html" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="B73" r:id="rId30" display="https://pchome.megatime.com.tw/stock/sid2704.html" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="B74" r:id="rId31" display="https://pchome.megatime.com.tw/stock/sid2704.html" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="B75" r:id="rId32" display="https://pchome.megatime.com.tw/stock/sid2723.html" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="B76" r:id="rId33" display="https://pchome.megatime.com.tw/stock/sid2723.html" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="B77" r:id="rId34" display="https://pchome.megatime.com.tw/stock/sid2727.html" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="B78" r:id="rId35" display="https://pchome.megatime.com.tw/stock/sid2727.html" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="B79" r:id="rId36" display="https://pchome.megatime.com.tw/stock/sid1259.html" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="B80" r:id="rId37" display="https://pchome.megatime.com.tw/stock/sid1259.html" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="B81" r:id="rId38" display="https://pchome.megatime.com.tw/stock/sid2729.html" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="B82" r:id="rId39" display="https://pchome.megatime.com.tw/stock/sid2729.html" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="B83" r:id="rId40" display="https://pchome.megatime.com.tw/stock/sid2347.html" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="B84" r:id="rId41" display="https://pchome.megatime.com.tw/stock/sid2347.html" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="B85" r:id="rId42" display="https://pchome.megatime.com.tw/stock/sid2362.html" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="B86" r:id="rId43" display="https://pchome.megatime.com.tw/stock/sid2362.html" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="B87" r:id="rId44" display="https://pchome.megatime.com.tw/stock/sid8044.html" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="B88" r:id="rId45" display="https://pchome.megatime.com.tw/stock/sid8044.html" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="B89" r:id="rId46" display="https://pchome.megatime.com.tw/stock/sid8454.html" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="B90" r:id="rId47" display="https://pchome.megatime.com.tw/stock/sid8454.html" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="B91" r:id="rId48" display="https://pchome.megatime.com.tw/stock/sid7722.html" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="B92" r:id="rId49" display="https://pchome.megatime.com.tw/stock/sid7722.html" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="70" orientation="landscape" r:id="rId50"/>
+  <pageSetup paperSize="9" scale="70" orientation="landscape" r:id="rId2"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="11" max="1048575" man="1"/>
   </colBreaks>
   <ignoredErrors>
     <ignoredError sqref="D31 H31:K31 J20" formula="1"/>
   </ignoredErrors>
-  <drawing r:id="rId51"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -17903,17 +15031,17 @@
       </c>
     </row>
     <row r="2" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="149"/>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149"/>
-      <c r="J2" s="149"/>
-      <c r="K2" s="149"/>
-      <c r="L2" s="149"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
       <c r="O2" s="15"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -22133,21 +19261,21 @@
       <c r="Y95" s="75"/>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B96" s="150"/>
-      <c r="C96" s="150"/>
-      <c r="D96" s="150"/>
-      <c r="E96" s="150"/>
-      <c r="F96" s="150"/>
-      <c r="G96" s="150"/>
-      <c r="H96" s="150"/>
-      <c r="I96" s="150"/>
-      <c r="J96" s="150"/>
-      <c r="K96" s="150"/>
-      <c r="L96" s="150"/>
-      <c r="M96" s="150"/>
-      <c r="N96" s="150"/>
-      <c r="O96" s="150"/>
-      <c r="P96" s="150"/>
+      <c r="B96" s="142"/>
+      <c r="C96" s="142"/>
+      <c r="D96" s="142"/>
+      <c r="E96" s="142"/>
+      <c r="F96" s="142"/>
+      <c r="G96" s="142"/>
+      <c r="H96" s="142"/>
+      <c r="I96" s="142"/>
+      <c r="J96" s="142"/>
+      <c r="K96" s="142"/>
+      <c r="L96" s="142"/>
+      <c r="M96" s="142"/>
+      <c r="N96" s="142"/>
+      <c r="O96" s="142"/>
+      <c r="P96" s="142"/>
       <c r="Q96" s="75"/>
       <c r="R96" s="75"/>
       <c r="S96" s="75"/>
@@ -22215,17 +19343,17 @@
       </c>
     </row>
     <row r="2" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="149"/>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149"/>
-      <c r="J2" s="149"/>
-      <c r="K2" s="149"/>
-      <c r="L2" s="149"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
       <c r="O2" s="15"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -26445,21 +23573,21 @@
       <c r="Y95" s="75"/>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B96" s="150"/>
-      <c r="C96" s="150"/>
-      <c r="D96" s="150"/>
-      <c r="E96" s="150"/>
-      <c r="F96" s="150"/>
-      <c r="G96" s="150"/>
-      <c r="H96" s="150"/>
-      <c r="I96" s="150"/>
-      <c r="J96" s="150"/>
-      <c r="K96" s="150"/>
-      <c r="L96" s="150"/>
-      <c r="M96" s="150"/>
-      <c r="N96" s="150"/>
-      <c r="O96" s="150"/>
-      <c r="P96" s="150"/>
+      <c r="B96" s="142"/>
+      <c r="C96" s="142"/>
+      <c r="D96" s="142"/>
+      <c r="E96" s="142"/>
+      <c r="F96" s="142"/>
+      <c r="G96" s="142"/>
+      <c r="H96" s="142"/>
+      <c r="I96" s="142"/>
+      <c r="J96" s="142"/>
+      <c r="K96" s="142"/>
+      <c r="L96" s="142"/>
+      <c r="M96" s="142"/>
+      <c r="N96" s="142"/>
+      <c r="O96" s="142"/>
+      <c r="P96" s="142"/>
       <c r="Q96" s="75"/>
       <c r="R96" s="75"/>
       <c r="S96" s="75"/>
@@ -26527,17 +23655,17 @@
       </c>
     </row>
     <row r="2" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="149"/>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149"/>
-      <c r="J2" s="149"/>
-      <c r="K2" s="149"/>
-      <c r="L2" s="149"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
       <c r="O2" s="15"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -30757,21 +27885,21 @@
       <c r="Y95" s="75"/>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B96" s="150"/>
-      <c r="C96" s="150"/>
-      <c r="D96" s="150"/>
-      <c r="E96" s="150"/>
-      <c r="F96" s="150"/>
-      <c r="G96" s="150"/>
-      <c r="H96" s="150"/>
-      <c r="I96" s="150"/>
-      <c r="J96" s="150"/>
-      <c r="K96" s="150"/>
-      <c r="L96" s="150"/>
-      <c r="M96" s="150"/>
-      <c r="N96" s="150"/>
-      <c r="O96" s="150"/>
-      <c r="P96" s="150"/>
+      <c r="B96" s="142"/>
+      <c r="C96" s="142"/>
+      <c r="D96" s="142"/>
+      <c r="E96" s="142"/>
+      <c r="F96" s="142"/>
+      <c r="G96" s="142"/>
+      <c r="H96" s="142"/>
+      <c r="I96" s="142"/>
+      <c r="J96" s="142"/>
+      <c r="K96" s="142"/>
+      <c r="L96" s="142"/>
+      <c r="M96" s="142"/>
+      <c r="N96" s="142"/>
+      <c r="O96" s="142"/>
+      <c r="P96" s="142"/>
       <c r="Q96" s="75"/>
       <c r="R96" s="75"/>
       <c r="S96" s="75"/>
@@ -30839,17 +27967,17 @@
       </c>
     </row>
     <row r="2" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="149"/>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149"/>
-      <c r="J2" s="149"/>
-      <c r="K2" s="149"/>
-      <c r="L2" s="149"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
       <c r="O2" s="15"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -35069,21 +32197,21 @@
       <c r="Y95" s="75"/>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B96" s="150"/>
-      <c r="C96" s="150"/>
-      <c r="D96" s="150"/>
-      <c r="E96" s="150"/>
-      <c r="F96" s="150"/>
-      <c r="G96" s="150"/>
-      <c r="H96" s="150"/>
-      <c r="I96" s="150"/>
-      <c r="J96" s="150"/>
-      <c r="K96" s="150"/>
-      <c r="L96" s="150"/>
-      <c r="M96" s="150"/>
-      <c r="N96" s="150"/>
-      <c r="O96" s="150"/>
-      <c r="P96" s="150"/>
+      <c r="B96" s="142"/>
+      <c r="C96" s="142"/>
+      <c r="D96" s="142"/>
+      <c r="E96" s="142"/>
+      <c r="F96" s="142"/>
+      <c r="G96" s="142"/>
+      <c r="H96" s="142"/>
+      <c r="I96" s="142"/>
+      <c r="J96" s="142"/>
+      <c r="K96" s="142"/>
+      <c r="L96" s="142"/>
+      <c r="M96" s="142"/>
+      <c r="N96" s="142"/>
+      <c r="O96" s="142"/>
+      <c r="P96" s="142"/>
       <c r="Q96" s="75"/>
       <c r="R96" s="75"/>
       <c r="S96" s="75"/>
@@ -35151,17 +32279,17 @@
       </c>
     </row>
     <row r="2" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="149"/>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149"/>
-      <c r="J2" s="149"/>
-      <c r="K2" s="149"/>
-      <c r="L2" s="149"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
       <c r="O2" s="15"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -39381,21 +36509,21 @@
       <c r="Y95" s="75"/>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B96" s="150"/>
-      <c r="C96" s="150"/>
-      <c r="D96" s="150"/>
-      <c r="E96" s="150"/>
-      <c r="F96" s="150"/>
-      <c r="G96" s="150"/>
-      <c r="H96" s="150"/>
-      <c r="I96" s="150"/>
-      <c r="J96" s="150"/>
-      <c r="K96" s="150"/>
-      <c r="L96" s="150"/>
-      <c r="M96" s="150"/>
-      <c r="N96" s="150"/>
-      <c r="O96" s="150"/>
-      <c r="P96" s="150"/>
+      <c r="B96" s="142"/>
+      <c r="C96" s="142"/>
+      <c r="D96" s="142"/>
+      <c r="E96" s="142"/>
+      <c r="F96" s="142"/>
+      <c r="G96" s="142"/>
+      <c r="H96" s="142"/>
+      <c r="I96" s="142"/>
+      <c r="J96" s="142"/>
+      <c r="K96" s="142"/>
+      <c r="L96" s="142"/>
+      <c r="M96" s="142"/>
+      <c r="N96" s="142"/>
+      <c r="O96" s="142"/>
+      <c r="P96" s="142"/>
       <c r="Q96" s="75"/>
       <c r="R96" s="75"/>
       <c r="S96" s="75"/>
@@ -39463,17 +36591,17 @@
       </c>
     </row>
     <row r="2" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="149"/>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149"/>
-      <c r="J2" s="149"/>
-      <c r="K2" s="149"/>
-      <c r="L2" s="149"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
       <c r="O2" s="15"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -43693,21 +40821,21 @@
       <c r="Y95" s="75"/>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B96" s="150"/>
-      <c r="C96" s="150"/>
-      <c r="D96" s="150"/>
-      <c r="E96" s="150"/>
-      <c r="F96" s="150"/>
-      <c r="G96" s="150"/>
-      <c r="H96" s="150"/>
-      <c r="I96" s="150"/>
-      <c r="J96" s="150"/>
-      <c r="K96" s="150"/>
-      <c r="L96" s="150"/>
-      <c r="M96" s="150"/>
-      <c r="N96" s="150"/>
-      <c r="O96" s="150"/>
-      <c r="P96" s="150"/>
+      <c r="B96" s="142"/>
+      <c r="C96" s="142"/>
+      <c r="D96" s="142"/>
+      <c r="E96" s="142"/>
+      <c r="F96" s="142"/>
+      <c r="G96" s="142"/>
+      <c r="H96" s="142"/>
+      <c r="I96" s="142"/>
+      <c r="J96" s="142"/>
+      <c r="K96" s="142"/>
+      <c r="L96" s="142"/>
+      <c r="M96" s="142"/>
+      <c r="N96" s="142"/>
+      <c r="O96" s="142"/>
+      <c r="P96" s="142"/>
       <c r="Q96" s="75"/>
       <c r="R96" s="75"/>
       <c r="S96" s="75"/>
@@ -43775,17 +40903,17 @@
       </c>
     </row>
     <row r="2" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="149"/>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149"/>
-      <c r="J2" s="149"/>
-      <c r="K2" s="149"/>
-      <c r="L2" s="149"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
       <c r="O2" s="15"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -48005,21 +45133,21 @@
       <c r="Y95" s="75"/>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B96" s="150"/>
-      <c r="C96" s="150"/>
-      <c r="D96" s="150"/>
-      <c r="E96" s="150"/>
-      <c r="F96" s="150"/>
-      <c r="G96" s="150"/>
-      <c r="H96" s="150"/>
-      <c r="I96" s="150"/>
-      <c r="J96" s="150"/>
-      <c r="K96" s="150"/>
-      <c r="L96" s="150"/>
-      <c r="M96" s="150"/>
-      <c r="N96" s="150"/>
-      <c r="O96" s="150"/>
-      <c r="P96" s="150"/>
+      <c r="B96" s="142"/>
+      <c r="C96" s="142"/>
+      <c r="D96" s="142"/>
+      <c r="E96" s="142"/>
+      <c r="F96" s="142"/>
+      <c r="G96" s="142"/>
+      <c r="H96" s="142"/>
+      <c r="I96" s="142"/>
+      <c r="J96" s="142"/>
+      <c r="K96" s="142"/>
+      <c r="L96" s="142"/>
+      <c r="M96" s="142"/>
+      <c r="N96" s="142"/>
+      <c r="O96" s="142"/>
+      <c r="P96" s="142"/>
       <c r="Q96" s="75"/>
       <c r="R96" s="75"/>
       <c r="S96" s="75"/>
@@ -48087,17 +45215,17 @@
       </c>
     </row>
     <row r="2" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="149"/>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149"/>
-      <c r="J2" s="149"/>
-      <c r="K2" s="149"/>
-      <c r="L2" s="149"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
       <c r="O2" s="15"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -52317,21 +49445,21 @@
       <c r="Y95" s="75"/>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B96" s="150"/>
-      <c r="C96" s="150"/>
-      <c r="D96" s="150"/>
-      <c r="E96" s="150"/>
-      <c r="F96" s="150"/>
-      <c r="G96" s="150"/>
-      <c r="H96" s="150"/>
-      <c r="I96" s="150"/>
-      <c r="J96" s="150"/>
-      <c r="K96" s="150"/>
-      <c r="L96" s="150"/>
-      <c r="M96" s="150"/>
-      <c r="N96" s="150"/>
-      <c r="O96" s="150"/>
-      <c r="P96" s="150"/>
+      <c r="B96" s="142"/>
+      <c r="C96" s="142"/>
+      <c r="D96" s="142"/>
+      <c r="E96" s="142"/>
+      <c r="F96" s="142"/>
+      <c r="G96" s="142"/>
+      <c r="H96" s="142"/>
+      <c r="I96" s="142"/>
+      <c r="J96" s="142"/>
+      <c r="K96" s="142"/>
+      <c r="L96" s="142"/>
+      <c r="M96" s="142"/>
+      <c r="N96" s="142"/>
+      <c r="O96" s="142"/>
+      <c r="P96" s="142"/>
       <c r="Q96" s="75"/>
       <c r="R96" s="75"/>
       <c r="S96" s="75"/>
@@ -52645,10 +49773,10 @@
         <v>138</v>
       </c>
       <c r="C1" s="13"/>
-      <c r="F1" s="157" t="s">
+      <c r="F1" s="143" t="s">
         <v>126</v>
       </c>
-      <c r="G1" s="157"/>
+      <c r="G1" s="143"/>
     </row>
     <row r="2" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
@@ -53295,17 +50423,17 @@
       </c>
     </row>
     <row r="2" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="149"/>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149"/>
-      <c r="J2" s="149"/>
-      <c r="K2" s="149"/>
-      <c r="L2" s="149"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
       <c r="O2" s="15"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -57525,21 +54653,21 @@
       <c r="Y95" s="75"/>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B96" s="150"/>
-      <c r="C96" s="150"/>
-      <c r="D96" s="150"/>
-      <c r="E96" s="150"/>
-      <c r="F96" s="150"/>
-      <c r="G96" s="150"/>
-      <c r="H96" s="150"/>
-      <c r="I96" s="150"/>
-      <c r="J96" s="150"/>
-      <c r="K96" s="150"/>
-      <c r="L96" s="150"/>
-      <c r="M96" s="150"/>
-      <c r="N96" s="150"/>
-      <c r="O96" s="150"/>
-      <c r="P96" s="150"/>
+      <c r="B96" s="142"/>
+      <c r="C96" s="142"/>
+      <c r="D96" s="142"/>
+      <c r="E96" s="142"/>
+      <c r="F96" s="142"/>
+      <c r="G96" s="142"/>
+      <c r="H96" s="142"/>
+      <c r="I96" s="142"/>
+      <c r="J96" s="142"/>
+      <c r="K96" s="142"/>
+      <c r="L96" s="142"/>
+      <c r="M96" s="142"/>
+      <c r="N96" s="142"/>
+      <c r="O96" s="142"/>
+      <c r="P96" s="142"/>
       <c r="Q96" s="75"/>
       <c r="R96" s="75"/>
       <c r="S96" s="75"/>
@@ -57607,17 +54735,17 @@
       </c>
     </row>
     <row r="2" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="149"/>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149"/>
-      <c r="J2" s="149"/>
-      <c r="K2" s="149"/>
-      <c r="L2" s="149"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
       <c r="O2" s="15"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -61837,21 +58965,21 @@
       <c r="Y95" s="75"/>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B96" s="150"/>
-      <c r="C96" s="150"/>
-      <c r="D96" s="150"/>
-      <c r="E96" s="150"/>
-      <c r="F96" s="150"/>
-      <c r="G96" s="150"/>
-      <c r="H96" s="150"/>
-      <c r="I96" s="150"/>
-      <c r="J96" s="150"/>
-      <c r="K96" s="150"/>
-      <c r="L96" s="150"/>
-      <c r="M96" s="150"/>
-      <c r="N96" s="150"/>
-      <c r="O96" s="150"/>
-      <c r="P96" s="150"/>
+      <c r="B96" s="142"/>
+      <c r="C96" s="142"/>
+      <c r="D96" s="142"/>
+      <c r="E96" s="142"/>
+      <c r="F96" s="142"/>
+      <c r="G96" s="142"/>
+      <c r="H96" s="142"/>
+      <c r="I96" s="142"/>
+      <c r="J96" s="142"/>
+      <c r="K96" s="142"/>
+      <c r="L96" s="142"/>
+      <c r="M96" s="142"/>
+      <c r="N96" s="142"/>
+      <c r="O96" s="142"/>
+      <c r="P96" s="142"/>
       <c r="Q96" s="75"/>
       <c r="R96" s="75"/>
       <c r="S96" s="75"/>
@@ -61919,17 +59047,17 @@
       </c>
     </row>
     <row r="2" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="149"/>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149"/>
-      <c r="J2" s="149"/>
-      <c r="K2" s="149"/>
-      <c r="L2" s="149"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
       <c r="O2" s="15"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -66149,21 +63277,21 @@
       <c r="Y95" s="75"/>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B96" s="150"/>
-      <c r="C96" s="150"/>
-      <c r="D96" s="150"/>
-      <c r="E96" s="150"/>
-      <c r="F96" s="150"/>
-      <c r="G96" s="150"/>
-      <c r="H96" s="150"/>
-      <c r="I96" s="150"/>
-      <c r="J96" s="150"/>
-      <c r="K96" s="150"/>
-      <c r="L96" s="150"/>
-      <c r="M96" s="150"/>
-      <c r="N96" s="150"/>
-      <c r="O96" s="150"/>
-      <c r="P96" s="150"/>
+      <c r="B96" s="142"/>
+      <c r="C96" s="142"/>
+      <c r="D96" s="142"/>
+      <c r="E96" s="142"/>
+      <c r="F96" s="142"/>
+      <c r="G96" s="142"/>
+      <c r="H96" s="142"/>
+      <c r="I96" s="142"/>
+      <c r="J96" s="142"/>
+      <c r="K96" s="142"/>
+      <c r="L96" s="142"/>
+      <c r="M96" s="142"/>
+      <c r="N96" s="142"/>
+      <c r="O96" s="142"/>
+      <c r="P96" s="142"/>
       <c r="Q96" s="75"/>
       <c r="R96" s="75"/>
       <c r="S96" s="75"/>
@@ -66231,17 +63359,17 @@
       </c>
     </row>
     <row r="2" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="149"/>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149"/>
-      <c r="J2" s="149"/>
-      <c r="K2" s="149"/>
-      <c r="L2" s="149"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
       <c r="O2" s="15"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -70461,21 +67589,21 @@
       <c r="Y95" s="75"/>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B96" s="150"/>
-      <c r="C96" s="150"/>
-      <c r="D96" s="150"/>
-      <c r="E96" s="150"/>
-      <c r="F96" s="150"/>
-      <c r="G96" s="150"/>
-      <c r="H96" s="150"/>
-      <c r="I96" s="150"/>
-      <c r="J96" s="150"/>
-      <c r="K96" s="150"/>
-      <c r="L96" s="150"/>
-      <c r="M96" s="150"/>
-      <c r="N96" s="150"/>
-      <c r="O96" s="150"/>
-      <c r="P96" s="150"/>
+      <c r="B96" s="142"/>
+      <c r="C96" s="142"/>
+      <c r="D96" s="142"/>
+      <c r="E96" s="142"/>
+      <c r="F96" s="142"/>
+      <c r="G96" s="142"/>
+      <c r="H96" s="142"/>
+      <c r="I96" s="142"/>
+      <c r="J96" s="142"/>
+      <c r="K96" s="142"/>
+      <c r="L96" s="142"/>
+      <c r="M96" s="142"/>
+      <c r="N96" s="142"/>
+      <c r="O96" s="142"/>
+      <c r="P96" s="142"/>
       <c r="Q96" s="75"/>
       <c r="R96" s="75"/>
       <c r="S96" s="75"/>
@@ -70543,17 +67671,17 @@
       </c>
     </row>
     <row r="2" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="149"/>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149"/>
-      <c r="J2" s="149"/>
-      <c r="K2" s="149"/>
-      <c r="L2" s="149"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
       <c r="O2" s="15"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -74773,21 +71901,21 @@
       <c r="Y95" s="75"/>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B96" s="150"/>
-      <c r="C96" s="150"/>
-      <c r="D96" s="150"/>
-      <c r="E96" s="150"/>
-      <c r="F96" s="150"/>
-      <c r="G96" s="150"/>
-      <c r="H96" s="150"/>
-      <c r="I96" s="150"/>
-      <c r="J96" s="150"/>
-      <c r="K96" s="150"/>
-      <c r="L96" s="150"/>
-      <c r="M96" s="150"/>
-      <c r="N96" s="150"/>
-      <c r="O96" s="150"/>
-      <c r="P96" s="150"/>
+      <c r="B96" s="142"/>
+      <c r="C96" s="142"/>
+      <c r="D96" s="142"/>
+      <c r="E96" s="142"/>
+      <c r="F96" s="142"/>
+      <c r="G96" s="142"/>
+      <c r="H96" s="142"/>
+      <c r="I96" s="142"/>
+      <c r="J96" s="142"/>
+      <c r="K96" s="142"/>
+      <c r="L96" s="142"/>
+      <c r="M96" s="142"/>
+      <c r="N96" s="142"/>
+      <c r="O96" s="142"/>
+      <c r="P96" s="142"/>
       <c r="Q96" s="75"/>
       <c r="R96" s="75"/>
       <c r="S96" s="75"/>
@@ -74855,17 +71983,17 @@
       </c>
     </row>
     <row r="2" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="149"/>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149"/>
-      <c r="J2" s="149"/>
-      <c r="K2" s="149"/>
-      <c r="L2" s="149"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
       <c r="O2" s="15"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -79085,21 +76213,21 @@
       <c r="Y95" s="75"/>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B96" s="150"/>
-      <c r="C96" s="150"/>
-      <c r="D96" s="150"/>
-      <c r="E96" s="150"/>
-      <c r="F96" s="150"/>
-      <c r="G96" s="150"/>
-      <c r="H96" s="150"/>
-      <c r="I96" s="150"/>
-      <c r="J96" s="150"/>
-      <c r="K96" s="150"/>
-      <c r="L96" s="150"/>
-      <c r="M96" s="150"/>
-      <c r="N96" s="150"/>
-      <c r="O96" s="150"/>
-      <c r="P96" s="150"/>
+      <c r="B96" s="142"/>
+      <c r="C96" s="142"/>
+      <c r="D96" s="142"/>
+      <c r="E96" s="142"/>
+      <c r="F96" s="142"/>
+      <c r="G96" s="142"/>
+      <c r="H96" s="142"/>
+      <c r="I96" s="142"/>
+      <c r="J96" s="142"/>
+      <c r="K96" s="142"/>
+      <c r="L96" s="142"/>
+      <c r="M96" s="142"/>
+      <c r="N96" s="142"/>
+      <c r="O96" s="142"/>
+      <c r="P96" s="142"/>
       <c r="Q96" s="75"/>
       <c r="R96" s="75"/>
       <c r="S96" s="75"/>
